--- a/tame_output/ON/bt/strategyON_20240615.xlsx
+++ b/tame_output/ON/bt/strategyON_20240615.xlsx
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.819117349151824</v>
+        <v>-4.819120127591237</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.243501081710214</v>
+        <v>1.243499970334449</v>
       </c>
       <c r="F1995" t="n">
         <v>0.08337066338413918</v>

--- a/tame_output/ON/bt/strategyON_20240615.xlsx
+++ b/tame_output/ON/bt/strategyON_20240615.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.8%</t>
+          <t>450.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-643.5%</t>
+          <t>-649.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-251.9%</t>
+          <t>-254.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.651662971301908</v>
+        <v>-4.710218886741063</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.138112189417669</v>
+        <v>1.114689823242007</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1696490937018327</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.654132677763714</v>
+        <v>-4.712688593202869</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.137196708206359</v>
+        <v>1.113774342030697</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1721188001636389</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.722502864087724</v>
+        <v>-4.781058779526879</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.120855556151457</v>
+        <v>1.097433189975795</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.162843101127424</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.831041045003858</v>
+        <v>-4.889596960443013</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.067876992416894</v>
+        <v>1.044454626241232</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.162843101127424</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.862034204332564</v>
+        <v>-4.920590119771719</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8801892937257989</v>
+        <v>0.8567669275501371</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.162843101127424</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.686559944540095</v>
+        <v>-4.745115859979249</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9549462296345741</v>
+        <v>0.9315238634589127</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.162843101127424</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.797496197181344</v>
+        <v>-4.856052112620498</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8863137573392816</v>
+        <v>0.86289139116362</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.162843101127424</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.805778271326402</v>
+        <v>-4.864334186765556</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8861323129011638</v>
+        <v>0.8627099467255022</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1711251752724823</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.745925652122679</v>
+        <v>-4.804481567561833</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9202457470147856</v>
+        <v>0.8968233808391239</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1711251752724823</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.659682189096301</v>
+        <v>-4.718238104535455</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9496894027991969</v>
+        <v>0.9262670366235353</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1711251752724823</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.704989008495281</v>
+        <v>-4.763544923934435</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9233424504841306</v>
+        <v>0.8999200843084689</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2119353382817131</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.734022113197582</v>
+        <v>-4.792578028636736</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9122810816363116</v>
+        <v>0.88885871546065</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2119353382817131</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.641211631746723</v>
+        <v>-4.699767547185877</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8786779661080211</v>
+        <v>0.8552555999323594</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1191248568308538</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.68560110107615</v>
+        <v>-4.744157016515304</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.862795654300851</v>
+        <v>0.8393732881251894</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1635143261602814</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.5729298828399</v>
+        <v>-4.631485798279054</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.902939850107074</v>
+        <v>0.8795174839314124</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.05084310792403124</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.460552881657227</v>
+        <v>-4.519108797096381</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9533819464108104</v>
+        <v>0.9299595802351488</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.05084310792403124</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.658787450543958</v>
+        <v>-4.717343365983112</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8855853206246571</v>
+        <v>0.8621629544489955</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2490776768107618</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.741788731569237</v>
+        <v>-4.800344647008391</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6907405282151988</v>
+        <v>0.6673181620395372</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2676485613379356</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.850402810012568</v>
+        <v>-4.908958725451722</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7674445575570721</v>
+        <v>0.7440221913814105</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2676485613379356</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.937001392993671</v>
+        <v>-4.995557308432825</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7473181504669539</v>
+        <v>0.7238957842912923</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2676485613379356</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.89861773043552</v>
+        <v>-4.957173645874674</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7600910568325829</v>
+        <v>0.7366686906569213</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2292648987797844</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.721501400400354</v>
+        <v>-4.780057315839508</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8276666176919514</v>
+        <v>0.8042442515162898</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2292648987797844</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.7665936452339</v>
+        <v>-4.825149560673053</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.810313111520446</v>
+        <v>0.7868907453447846</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2911609419491742</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.587218223995132</v>
+        <v>-4.645774139434286</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8758502553223675</v>
+        <v>0.8524278891467061</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1343841837784555</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.632232437515738</v>
+        <v>-4.690788352954891</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.838652025245715</v>
+        <v>0.8152296590700534</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1647330790930601</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.899236947788173</v>
+        <v>-4.957792863227326</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7375417834756868</v>
+        <v>0.7141194173000251</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3590961171360087</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.000434729225345</v>
+        <v>-5.058990644664499</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6962665927973191</v>
+        <v>0.6728442266216574</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4275049306813279</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.967959143054573</v>
+        <v>-5.026515058493727</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7068567888199446</v>
+        <v>0.6834344226442832</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4275049306813279</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.948921015347276</v>
+        <v>-5.00747693078643</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7109967591111086</v>
+        <v>0.687574392935447</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4856885420125224</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.980047646497894</v>
+        <v>-5.038603561937048</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8761279755895417</v>
+        <v>0.8527056094138801</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4856885420125224</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.032368027098686</v>
+        <v>-5.09092394253784</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8560331523353586</v>
+        <v>0.8326107861596972</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4507416820036503</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.052625325627644</v>
+        <v>-5.111181241066798</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8539387633207012</v>
+        <v>0.8305163971450398</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4507416820036503</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.904882355392641</v>
+        <v>-4.963438270831795</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9921885992067243</v>
+        <v>0.9687662330310627</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2829343247687671</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.006897037923863</v>
+        <v>-5.065452953363017</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9541763477257168</v>
+        <v>0.9307539815500552</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2829343247687671</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.000744331871078</v>
+        <v>-5.059300247310232</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9572997785384889</v>
+        <v>0.9338774123628273</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2767816187159828</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.01755363002158</v>
+        <v>-5.076109545460734</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9496565360183982</v>
+        <v>0.9262341698427368</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2935909168664845</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.955255631245458</v>
+        <v>-5.013811546684612</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.040911289325668</v>
+        <v>1.017488923150006</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2935909168664845</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.7534654335803</v>
+        <v>-4.812021349019454</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8302082407811293</v>
+        <v>0.8067858746054677</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.09557272469733008</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.693574751937707</v>
+        <v>-4.752130667376861</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9244547457603418</v>
+        <v>0.9010323795846804</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.0356820430547366</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.791315296562681</v>
+        <v>-4.849871212001835</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8999862640263958</v>
+        <v>0.8765638978507342</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.05157132118771679</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.96765305668561</v>
+        <v>-5.026208972124764</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8279871408018957</v>
+        <v>0.8045647746262343</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2279090813106462</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.896106733908733</v>
+        <v>-4.954662649347887</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8550972879525751</v>
+        <v>0.8316749217769135</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2279090813106462</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.851733602270165</v>
+        <v>-4.910289517709319</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8727094080434388</v>
+        <v>0.8492870418677771</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1835359496720776</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.843779631975393</v>
+        <v>-4.902335547414546</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8758909961613477</v>
+        <v>0.8524686299856861</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1835359496720776</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.796123901414337</v>
+        <v>-4.854679816853491</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9013350454135747</v>
+        <v>0.8779126792379131</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1358802191110219</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.66843959162004</v>
+        <v>-4.726995507059194</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9573011427060178</v>
+        <v>0.9338787765303564</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.00819590931672548</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.729106182022429</v>
+        <v>-4.787662097461583</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9197891790209347</v>
+        <v>0.8963668128452731</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.08989422603525915</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.68426778041403</v>
+        <v>-4.742823695853184</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9418222422749227</v>
+        <v>0.9183998760992611</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.08535079309038968</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.785026416171029</v>
+        <v>-4.843582331610182</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9056797276032014</v>
+        <v>0.88225736142754</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.1741763618173951</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.740823579085128</v>
+        <v>-4.799379494524282</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9292404649653987</v>
+        <v>0.9058180987897373</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1299735247314946</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.777802606748571</v>
+        <v>-4.836358522187725</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9128588543692693</v>
+        <v>0.8894364881936077</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.09299962294016412</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.797860685613411</v>
+        <v>-4.856416601052565</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9560833880063726</v>
+        <v>0.932661021830711</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.09299962294016412</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.757930012435521</v>
+        <v>-4.816485927874675</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9704963618717819</v>
+        <v>0.9470739956961203</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.05306894976227378</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.717459664872816</v>
+        <v>-4.77601558031197</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9816327291351339</v>
+        <v>0.9582103629594723</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.01259860219956882</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.652235483745611</v>
+        <v>-4.710791399184765</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.024909805678721</v>
+        <v>1.001487439503059</v>
       </c>
       <c r="F1988" t="n">
         <v>0.05262557892763681</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.702729774102667</v>
+        <v>-4.761285689541821</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.000673061835179</v>
+        <v>0.9772506956595173</v>
       </c>
       <c r="F1989" t="n">
         <v>0.007604841801562567</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.722841430137375</v>
+        <v>-4.781397345576529</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9938851917525358</v>
+        <v>0.9704628255768744</v>
       </c>
       <c r="F1990" t="n">
         <v>0.01863218679898176</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.820522009410022</v>
+        <v>-4.879077924849176</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.115370731064688</v>
+        <v>1.091948364889026</v>
       </c>
       <c r="F1991" t="n">
         <v>-0.09207100854120703</v>
@@ -47367,10 +47367,10 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.796730440803879</v>
+        <v>-4.855286356243033</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.245000267724962</v>
+        <v>1.221577901549301</v>
       </c>
       <c r="F1992" t="n">
         <v>-0.06827943993506475</v>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.833484859365601</v>
+        <v>-4.892040774804755</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.222006476314133</v>
+        <v>1.198584110138471</v>
       </c>
       <c r="F1993" t="n">
         <v>-0.06827943993506475</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.829150556308553</v>
+        <v>-4.887706471747707</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.221933393120731</v>
+        <v>1.19851102694507</v>
       </c>
       <c r="F1994" t="n">
         <v>0.08337066338413918</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.76118365476374</v>
+        <v>3.563707177477392</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.819120127591237</v>
+        <v>-4.878814010354424</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.243499970334449</v>
+        <v>1.219622417229174</v>
       </c>
       <c r="F1995" t="n">
         <v>0.08337066338413918</v>

--- a/tame_output/ON/bt/strategyON_20240615.xlsx
+++ b/tame_output/ON/bt/strategyON_20240615.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>-6.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-693.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.2%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.5%</t>
+          <t>-658.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-277.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-254.3%</t>
+          <t>-270.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.1%</t>
+          <t>-156.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-215.7%</t>
+          <t>-220.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-123.9%</t>
+          <t>-138.8%</t>
         </is>
       </c>
     </row>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5908024501953608</v>
+        <v>-0.5976218536861235</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.889803315145894</v>
+        <v>2.887075553749589</v>
       </c>
       <c r="F1843" t="n">
         <v>1.455613419548912</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6725743506231125</v>
+        <v>-0.6793937541138753</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.847177280930031</v>
+        <v>2.844449519533726</v>
       </c>
       <c r="F1844" t="n">
         <v>1.482648992955049</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7397834584949903</v>
+        <v>-0.746602861985753</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.825058954614982</v>
+        <v>2.822331193218677</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9473492428866022</v>
+        <v>-0.9541686463773649</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.739857436977578</v>
+        <v>2.737129675581273</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.365103266433439</v>
+        <v>-1.371922669924202</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.570682719063906</v>
+        <v>2.567954957667602</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.65523493303887</v>
+        <v>-1.662054336529633</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.454496269020656</v>
+        <v>2.451768507624351</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8814109797567796</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.863238991391948</v>
+        <v>-1.870058394882711</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.37618679023335</v>
+        <v>2.373459028837045</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8814109797567796</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.074651412279923</v>
+        <v>-2.081470815770686</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.286703278216148</v>
+        <v>2.283975516819843</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6699985588688046</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.440720139424576</v>
+        <v>-2.447539542915339</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.133360086664736</v>
+        <v>2.130632325268431</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3039298317241519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.649210920876261</v>
+        <v>-2.656030324367023</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.07030206382283</v>
+        <v>2.067574302426525</v>
       </c>
       <c r="F1852" t="n">
         <v>0.09543905027246746</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.896412105641482</v>
+        <v>-2.903231509132245</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.97952034032531</v>
+        <v>1.976792578929005</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1155924037712799</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.388797133665579</v>
+        <v>-3.395616537156342</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.783672721159404</v>
+        <v>1.780944959763099</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3767926242528168</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.773977524595651</v>
+        <v>-3.780796928086414</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.628143103600238</v>
+        <v>1.625415342203933</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117660297822314</v>
+        <v>-4.124479701313077</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492439117764189</v>
+        <v>1.489711356367884</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.324172074709336</v>
+        <v>-4.330991478200098</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.405940465665638</v>
+        <v>1.403212704269333</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.643516149789837</v>
+        <v>-4.6503355532806</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.279975762333697</v>
+        <v>1.277248000937392</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.075321942939625</v>
+        <v>-5.082141346430388</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.093586332541187</v>
+        <v>1.090858571144881</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.310015937072177</v>
+        <v>-5.31683534056294</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9879935098902566</v>
+        <v>0.9852657484939513</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.64567858430263</v>
+        <v>-5.652497987793392</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8523090426540407</v>
+        <v>0.8495812812577355</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.009304829202943</v>
+        <v>-6.016124232693706</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7133461049281569</v>
+        <v>0.7106183435318516</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.381251615332452</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.5638219054821842</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.789840392513131</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.3991479386246719</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-7.066416492828964</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.2837029309697994</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.482808367115961</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.1151402318638777</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.746755052717844</v>
+        <v>-7.753574456208606</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01982024829180373</v>
+        <v>0.01709248689549892</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.092629874702652</v>
+        <v>-8.099449278193415</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1224301153564245</v>
+        <v>-0.1251578767527293</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.256209752887036</v>
+        <v>-8.263029156377799</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1894571465751773</v>
+        <v>-0.1921849079714821</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.552871094697235</v>
+        <v>-8.559690498187997</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3043427073700484</v>
+        <v>-0.3070704687663532</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.739590803006537</v>
+        <v>-8.7464102064973</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3830568952281723</v>
+        <v>-0.3857846566244776</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.122592191749169</v>
+        <v>-9.129411595239931</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5363595520468092</v>
+        <v>-0.539087313443114</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.304461982734203</v>
+        <v>-9.311281386224966</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6065359524693927</v>
+        <v>-0.609263713865698</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.663992305238205</v>
+        <v>-9.670811708728968</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7449977781729431</v>
+        <v>-0.7477255395692484</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714341368692427</v>
+        <v>-9.72116077218319</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7572213835974546</v>
+        <v>-0.7599491449937594</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.811960646113823</v>
+        <v>-9.818780049604586</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7932273439442441</v>
+        <v>-0.7959551053405494</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959486734119466</v>
+        <v>-9.966306137610228</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8493442228249291</v>
+        <v>-0.8520719842212343</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-10.17056431294009</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.9282620572345373</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23807788570949</v>
+        <v>-10.24489728920026</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9507849318578621</v>
+        <v>-0.9535126932541673</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.442858704874723</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.16460805404204</v>
+        <v>-10.17142745753281</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.906025297697461</v>
+        <v>-0.9087530590937662</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.369388873207274</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33973247142859</v>
+        <v>-10.34655187491935</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9615198439045614</v>
+        <v>-0.9642476053008666</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.544513290593818</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.57418456544308</v>
+        <v>-10.58100396893384</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.062519846411953</v>
+        <v>-1.065247607808259</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.544513290593818</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.67855929646952</v>
+        <v>-10.68537869996029</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.110941929596508</v>
+        <v>-1.113669690992813</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.648888021620264</v>
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.73134545206985</v>
+        <v>-10.75967076365823</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.130940601998082</v>
+        <v>-1.142270726633432</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.744563508202661</v>
+        <v>-2.788762539460297</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.515215898222009</v>
+        <v>1.488696479467427</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.85738224543814</v>
+        <v>-10.88570755702652</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.178661590716283</v>
+        <v>-1.189991715351634</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.719311885392918</v>
+        <v>-2.763510916650554</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.533060600536969</v>
+        <v>1.506541181782387</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.80536673146933</v>
+        <v>-10.8336920430577</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.153865049442357</v>
+        <v>-1.165195174077708</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.719311885392918</v>
+        <v>-2.763510916650554</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.53705093622337</v>
+        <v>1.510531517468788</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.94703857319345</v>
+        <v>-10.97536388478182</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.212009013030747</v>
+        <v>-1.223339137666097</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.719311885392918</v>
+        <v>-2.763510916650554</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.535575709324628</v>
+        <v>1.509056290570047</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.89744772876861</v>
+        <v>-10.92577304035699</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.177119265095941</v>
+        <v>-1.188449389731292</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.669721040968084</v>
+        <v>-2.71392007222572</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.580383626144401</v>
+        <v>1.553864207389819</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.88464033576384</v>
+        <v>-10.91296564735221</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.185047441540715</v>
+        <v>-1.196377566176065</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.718576815976986</v>
+        <v>-2.762775847234621</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.538019027492377</v>
+        <v>1.511499608737796</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.65879518304443</v>
+        <v>-10.6871204946328</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.085130307416742</v>
+        <v>-1.096460432052092</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.676650140389822</v>
+        <v>-2.720849171647457</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.572754105880884</v>
+        <v>1.546234687126303</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.53421652670684</v>
+        <v>-10.56254183829521</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.034159700325647</v>
+        <v>-1.045489824960997</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.676650140389822</v>
+        <v>-2.720849171647457</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.573893250436943</v>
+        <v>1.547373831682362</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.58711181475112</v>
+        <v>-10.6154371263395</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.052684041381253</v>
+        <v>-1.064014166016603</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.671694794301376</v>
+        <v>-2.715893825559011</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.579500232252118</v>
+        <v>1.552980813497537</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.51497863946324</v>
+        <v>-10.54330395105162</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.018097067027464</v>
+        <v>-1.029427191662815</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.671694794301376</v>
+        <v>-2.715893825559011</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.585233936490755</v>
+        <v>1.558714517736173</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.4436122468536</v>
+        <v>-10.47193755844197</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9992877723774711</v>
+        <v>-1.010617897012821</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.600328401691728</v>
+        <v>-2.644527432949363</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.618316509662678</v>
+        <v>1.591797090908097</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17977537964953</v>
+        <v>-10.2081006912379</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9036365068087506</v>
+        <v>-0.9149666314441007</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.600328401691728</v>
+        <v>-2.644527432949363</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.608433028349771</v>
+        <v>1.58191360959519</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.912533578781128</v>
+        <v>-9.940858890369503</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7985743469607649</v>
+        <v>-0.809904471596115</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.600328401691728</v>
+        <v>-2.644527432949363</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.606598467850397</v>
+        <v>1.580079049095816</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.814626540104637</v>
+        <v>-9.842951851693012</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7597118464636297</v>
+        <v>-0.7710419710989798</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.532342651831171</v>
+        <v>-2.576541683088807</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.64708960279327</v>
+        <v>1.620570184038689</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.790672999128679</v>
+        <v>-9.818998310717054</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7494619239277527</v>
+        <v>-0.7607920485631028</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.508389110855214</v>
+        <v>-2.552588142112849</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.662130233524338</v>
+        <v>1.635610814769757</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.526613060805882</v>
+        <v>-9.554938372394258</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6570982647603865</v>
+        <v>-0.6684283893957366</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.244329172532418</v>
+        <v>-2.288528203790053</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.807305880356264</v>
+        <v>1.780786461601682</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.819533437301045</v>
+        <v>-8.84785874888942</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.377053449018752</v>
+        <v>-0.3883835736541021</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.244329172532418</v>
+        <v>-2.288528203790053</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.804518846695963</v>
+        <v>1.777999427941382</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.779349138934855</v>
+        <v>-8.80767445052323</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3606361057844345</v>
+        <v>-0.3719662304197846</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.204144874166227</v>
+        <v>-2.248343905423862</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.828973049603519</v>
+        <v>1.802453630848937</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.615949267995493</v>
+        <v>-8.644274579583868</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.295909336187933</v>
+        <v>-0.3072394608232831</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.040745003226864</v>
+        <v>-2.0849440344845</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.926379793387893</v>
+        <v>1.899860374633312</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.382468045765894</v>
+        <v>-8.410793357354269</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.194592418458241</v>
+        <v>-0.2059225430935911</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.807263780997266</v>
+        <v>-1.851462812254901</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.074392955563504</v>
+        <v>2.047873536808924</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.232801654758379</v>
+        <v>-8.261126966346755</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1376180723681943</v>
+        <v>-0.1489481970035444</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.71436028975473</v>
+        <v>-1.758559321012365</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.127242839996067</v>
+        <v>2.100723421241486</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.100526181127492</v>
+        <v>-8.128851492715867</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0893403961688124</v>
+        <v>-0.1006705208041625</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.582084816123843</v>
+        <v>-1.626283847381479</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.201975610921626</v>
+        <v>2.175456192167045</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.909926506454339</v>
+        <v>-7.938251818042715</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0102854656119149</v>
+        <v>-0.021615590247265</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.39148514145069</v>
+        <v>-1.435684172708326</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.319150476413154</v>
+        <v>2.292631057658573</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.660926707770758</v>
+        <v>-7.689252019359134</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1022207950851763</v>
+        <v>0.09089067044982624</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.39148514145069</v>
+        <v>-1.435684172708326</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.332056817636813</v>
+        <v>2.305537398882232</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.766516697543863</v>
+        <v>-7.794842009132238</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.06799113042328386</v>
+        <v>-0.07932125505863397</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.497075131223795</v>
+        <v>-1.54127416248143</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.140726894173732</v>
+        <v>2.114207475419151</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.78525159966246</v>
+        <v>-7.813576911250835</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.02694074939363666</v>
+        <v>-0.03827087402898677</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.502671140883926</v>
+        <v>-1.546870172141561</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.185913630254739</v>
+        <v>2.159394211500159</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.637311558254861</v>
+        <v>-7.665636869843236</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.08764365551876452</v>
+        <v>-0.09897378015411462</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.482350224975368</v>
+        <v>-1.526549256233004</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.078227257111707</v>
+        <v>2.051707838357125</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.584342036000872</v>
+        <v>-7.612667347589247</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.07516983287064694</v>
+        <v>-0.08649995750599704</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.473579733979015</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.101294984210622</v>
+        <v>2.07477556545604</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.540793629230182</v>
+        <v>-7.569118940818557</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.06471108225746391</v>
+        <v>-0.07604120689281402</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.473579733979015</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.094334372115529</v>
+        <v>2.067814953360947</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.298645235776323</v>
+        <v>-7.326970547364699</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04661062950522243</v>
+        <v>0.03528050486987233</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.473579733979015</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.108796726496672</v>
+        <v>2.08227730774209</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.190386098653802</v>
+        <v>-7.218711410242177</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.08444640481342613</v>
+        <v>0.07311628017807603</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.429380702721379</v>
+        <v>-1.473579733979015</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.103328846955867</v>
+        <v>2.076809428201285</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.067094963836671</v>
+        <v>-7.095420275425046</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1312609527508553</v>
+        <v>0.1199308281155052</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.306089567904249</v>
+        <v>-1.350288599161884</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.174801621856722</v>
+        <v>2.14828220310214</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.045945764933228</v>
+        <v>-7.074271076521603</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1474216105495576</v>
+        <v>0.1360914859142075</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.284940369000806</v>
+        <v>-1.329139400258441</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.195192119436113</v>
+        <v>2.168672700681532</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.802180322949783</v>
+        <v>-6.830505634538159</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2407084956899861</v>
+        <v>0.229378371054636</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.284940369000806</v>
+        <v>-1.329139400258441</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.190972827783164</v>
+        <v>2.164453409028583</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.700417502672488</v>
+        <v>-6.728742814260864</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.28353793772092</v>
+        <v>0.2722078130855698</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.315920331866012</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.201028582738637</v>
+        <v>2.174509163984056</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.450567108723414</v>
+        <v>-6.478892420311789</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.376220170284252</v>
+        <v>0.3648900456489019</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.315920331866012</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.193770657722339</v>
+        <v>2.167251238967758</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.274675016255982</v>
+        <v>-6.303000327844357</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4501761307918737</v>
+        <v>0.4388460061565236</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.315920331866012</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.197369781242988</v>
+        <v>2.170850362488407</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.103228553233518</v>
+        <v>-6.131553864821893</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5320822220554127</v>
+        <v>0.5207520974200626</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.100274837585914</v>
+        <v>-1.144473868843549</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.31356516511102</v>
+        <v>2.287045746356438</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.878195553564695</v>
+        <v>-5.906520865153071</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6211158995392387</v>
+        <v>0.6097857749038886</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8752418379170909</v>
+        <v>-0.9194408691747263</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.44760544252861</v>
+        <v>2.421086023774029</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.814559811330761</v>
+        <v>-5.842885122919136</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6512649974871301</v>
+        <v>0.63993487285178</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8116060956831563</v>
+        <v>-0.8558051269407918</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.490481688923288</v>
+        <v>2.463962270168707</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.770797630024919</v>
+        <v>-5.799122941613295</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.649964128793262</v>
+        <v>0.6386340041579119</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8116060956831563</v>
+        <v>-0.8558051269407918</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.471675947707084</v>
+        <v>2.445156528952503</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.530367133220059</v>
+        <v>-5.558692444808434</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7478794041400838</v>
+        <v>0.7365492795047337</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5711755988782961</v>
+        <v>-0.6153746301359315</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.617677322414877</v>
+        <v>2.591157903660296</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.458124565048864</v>
+        <v>-5.48644987663724</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7807057452433819</v>
+        <v>0.7693756206080318</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5711755988782961</v>
+        <v>-0.6153746301359315</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.621606636249697</v>
+        <v>2.595087217495116</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.405126242767476</v>
+        <v>-5.433451554355852</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.802583658073277</v>
+        <v>0.7912535334379269</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5158393398763572</v>
+        <v>-0.5600383711339927</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.655486975568201</v>
+        <v>2.628967556813619</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.296321357287749</v>
+        <v>-5.324646668876125</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8431036834851611</v>
+        <v>0.831773558849811</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5158393398763572</v>
+        <v>-0.5600383711339927</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.652485046788194</v>
+        <v>2.625965628033613</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.076300559250739</v>
+        <v>-5.104625870839114</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9326910397105794</v>
+        <v>0.9213609150752293</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.374619494808377</v>
+        <v>-0.4188185260660124</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.738795990839597</v>
+        <v>2.712276572085015</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.943432870187461</v>
+        <v>-4.971758181775837</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.001732298137714</v>
+        <v>0.9904021735023638</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.374619494808377</v>
+        <v>-0.4188185260660124</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.75469017364142</v>
+        <v>2.728170754886838</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.823259786822963</v>
+        <v>-4.851585098411338</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.050947375923815</v>
+        <v>1.039617251288465</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.254446411443878</v>
+        <v>-0.2986454427015135</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.827939868100421</v>
+        <v>2.80142044934584</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.678587641723225</v>
+        <v>-4.7069129533116</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.11890433652515</v>
+        <v>1.1075742118898</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1097742663441406</v>
+        <v>-0.1539732976017761</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.924831257721703</v>
+        <v>2.898311838967122</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.738462469080917</v>
+        <v>-4.766787780669293</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.080991896983499</v>
+        <v>1.069661772348149</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1696490937018327</v>
+        <v>-0.2138481249594682</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.874943852708514</v>
+        <v>2.848424433953933</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.710218886741063</v>
+        <v>-4.679988282890283</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.114689823242007</v>
+        <v>1.126782064782319</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1696490937018327</v>
+        <v>-0.2138481249594682</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.89734434603108</v>
+        <v>2.870824927276499</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.712688593202869</v>
+        <v>-4.682457989352089</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.113774342030697</v>
+        <v>1.125866583571008</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1721188001636389</v>
+        <v>-0.2163178314212744</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.895934923527408</v>
+        <v>2.869415504772827</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.781058779526879</v>
+        <v>-4.7508281756761</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.097433189975795</v>
+        <v>1.109525431516106</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.2070421323850594</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.91250726542384</v>
+        <v>2.885987846669258</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.889596960443013</v>
+        <v>-4.859366356592234</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.044454626241232</v>
+        <v>1.056546867781544</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.2070421323850594</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.902943974055731</v>
+        <v>2.87642455530115</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.920590119771719</v>
+        <v>-4.890359515920939</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8567669275501371</v>
+        <v>0.8688591690904488</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.2070421323850594</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.727653539096118</v>
+        <v>2.701134120341536</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.745115859979249</v>
+        <v>-4.71488525612847</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9315238634589127</v>
+        <v>0.943616104999224</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.2070421323850594</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.732220771087905</v>
+        <v>2.705701352333324</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.856052112620498</v>
+        <v>-4.825821508769719</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.86289139116362</v>
+        <v>0.8749836327039315</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.2070421323850594</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.707962799849112</v>
+        <v>2.681443381094531</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.864334186765556</v>
+        <v>-4.834103582914778</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8627099467255022</v>
+        <v>0.8748021882658137</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.2153242065301178</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.706124940581983</v>
+        <v>2.679605521827402</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.804481567561833</v>
+        <v>-4.774250963711054</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8968233808391239</v>
+        <v>0.9089156223794355</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.2153242065301178</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.716297327014115</v>
+        <v>2.689777908259534</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.718238104535455</v>
+        <v>-4.688007500684677</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9262670366235353</v>
+        <v>0.9383592781638468</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.2153242065301178</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.711243597587976</v>
+        <v>2.684724178833394</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.763544923934435</v>
+        <v>-4.733314320083656</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8999200843084689</v>
+        <v>0.9120123258487804</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2119353382817131</v>
+        <v>-0.2561343695393486</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.678533275226963</v>
+        <v>2.652013856472381</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.792578028636736</v>
+        <v>-4.762347424785958</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.88885871546065</v>
+        <v>0.9009509570009615</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2119353382817131</v>
+        <v>-0.2561343695393486</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.679085148260064</v>
+        <v>2.652565729505483</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.699767547185877</v>
+        <v>-4.669536943335098</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8552555999323594</v>
+        <v>0.867347841472671</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1191248568308538</v>
+        <v>-0.1633238880884892</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.664044129021946</v>
+        <v>2.637524710267364</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.744157016515304</v>
+        <v>-4.713926412664526</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8393732881251894</v>
+        <v>0.8514655296655009</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1635143261602814</v>
+        <v>-0.2077133574179169</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.63928392334889</v>
+        <v>2.612764504594308</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.631485798279054</v>
+        <v>-4.601255194428275</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8795174839314124</v>
+        <v>0.8916097254717239</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.05084310792403124</v>
+        <v>-0.09504213918166671</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.701962362802363</v>
+        <v>2.675442944047782</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.519108797096381</v>
+        <v>-4.488878193245602</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9299595802351488</v>
+        <v>0.9420518217754603</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.05084310792403124</v>
+        <v>-0.09504213918166671</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.70745365863303</v>
+        <v>2.680934239878449</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.717343365983112</v>
+        <v>-4.687112762132333</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8621629544489955</v>
+        <v>0.874255195989307</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2490776768107618</v>
+        <v>-0.2932767080683973</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.600010119069531</v>
+        <v>2.57349070031495</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.800344647008391</v>
+        <v>-4.770114043157612</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6673181620395372</v>
+        <v>0.6794104035798487</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2676485613379356</v>
+        <v>-0.311847592595571</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.42722330835388</v>
+        <v>2.400703889599299</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.908958725451722</v>
+        <v>-4.878728121600943</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7440221913814105</v>
+        <v>0.756114432921722</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2676485613379356</v>
+        <v>-0.311847592595571</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.547372969073086</v>
+        <v>2.520853550318504</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.995557308432825</v>
+        <v>-4.965326704582046</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7238957842912923</v>
+        <v>0.7359880258316038</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2676485613379356</v>
+        <v>-0.311847592595571</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.561885995175408</v>
+        <v>2.535366576420827</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.957173645874674</v>
+        <v>-4.926943042023895</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7366686906569213</v>
+        <v>0.7487609321972328</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2292648987797844</v>
+        <v>-0.2734639300374199</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.582335634052668</v>
+        <v>2.555816215298087</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.780057315839508</v>
+        <v>-4.749826711988729</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8042442515162898</v>
+        <v>0.8163364930566013</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2292648987797844</v>
+        <v>-0.2734639300374199</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.57906466289797</v>
+        <v>2.552545244143388</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.825149560673053</v>
+        <v>-4.794918956822275</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7868907453447846</v>
+        <v>0.7989829868850959</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2911609419491742</v>
+        <v>-0.3353599732068097</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.542610428758249</v>
+        <v>2.516091010003668</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.645774139434286</v>
+        <v>-4.615543535583507</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8524278891467061</v>
+        <v>0.8645201306870174</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1343841837784555</v>
+        <v>-0.178583215036091</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.630463458967094</v>
+        <v>2.603944040212513</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.690788352954891</v>
+        <v>-4.660557749104113</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8152296590700534</v>
+        <v>0.8273219006103649</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1647330790930601</v>
+        <v>-0.2089321103506956</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.593061577109922</v>
+        <v>2.56654215835534</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.957792863227326</v>
+        <v>-4.927562259376548</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7141194173000251</v>
+        <v>0.7262116588403367</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3590961171360087</v>
+        <v>-0.4032951483936442</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.482135316623098</v>
+        <v>2.455615897868517</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.058990644664499</v>
+        <v>-5.028760040813721</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6728442266216574</v>
+        <v>0.6849364681619692</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4275049306813279</v>
+        <v>-0.4717039619389634</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.440293950392408</v>
+        <v>2.413774531637827</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.026515058493727</v>
+        <v>-4.996284454642948</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6834344226442832</v>
+        <v>0.6955266641845945</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4275049306813279</v>
+        <v>-0.4717039619389634</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.437893911946725</v>
+        <v>2.411374493192143</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.00747693078643</v>
+        <v>-4.977246326935651</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.687574392935447</v>
+        <v>0.6996666344757585</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4856885420125224</v>
+        <v>-0.5298875732701579</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.399508464356253</v>
+        <v>2.372989045601672</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.745557904434113</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.038603561937048</v>
+        <v>-4.975284103488473</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8527056094138801</v>
+        <v>0.7550878387249762</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4856885420125224</v>
+        <v>-0.5298875732701579</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.577090333294934</v>
+        <v>2.427625360472018</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.746391233420246</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.09092394253784</v>
+        <v>-5.027604484089265</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8326107861596972</v>
+        <v>0.7349930154707929</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4507416820036503</v>
+        <v>-0.4949407132612857</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.598891778286391</v>
+        <v>2.449426805463475</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.752399763817172</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.111181241066798</v>
+        <v>-5.047861782618223</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8305163971450398</v>
+        <v>0.7328986264561359</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4507416820036503</v>
+        <v>-0.4949407132612857</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.604900308683316</v>
+        <v>2.455435335860401</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.831552411609194</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.963438270831795</v>
+        <v>-4.90011881238322</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9687662330310627</v>
+        <v>0.8711484623421588</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2829343247687671</v>
+        <v>-0.3271333560264026</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.784737370816268</v>
+        <v>2.635272397993353</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.834346033140675</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.065452953363017</v>
+        <v>-5.002133494914442</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9307539815500552</v>
+        <v>0.8331362108611513</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2829343247687671</v>
+        <v>-0.3271333560264026</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.787530992347749</v>
+        <v>2.638066019524834</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.835008381532333</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.059300247310232</v>
+        <v>-4.995980788861657</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9338774123628273</v>
+        <v>0.8362596416739234</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2767816187159828</v>
+        <v>-0.3209806499736183</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.791884964371078</v>
+        <v>2.642419991548163</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.834088858272444</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.076109545460734</v>
+        <v>-5.012790087012159</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9262341698427368</v>
+        <v>0.8286163991538329</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2935909168664845</v>
+        <v>-0.3377899481241199</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.780879862220887</v>
+        <v>2.631414889397972</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>2.900424412069265</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.013811546684612</v>
+        <v>-4.950492088236037</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.017488923150006</v>
+        <v>0.9198711524611025</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2935909168664845</v>
+        <v>-0.3377899481241199</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.847215416017708</v>
+        <v>2.697750443194793</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.609005284458663</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.812021349019454</v>
+        <v>-4.748701890570879</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8067858746054677</v>
+        <v>0.7091681039165638</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.09557272469733008</v>
+        <v>-0.1397717559549655</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.674607203708599</v>
+        <v>2.525142230885684</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.679295516780838</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.752130667376861</v>
+        <v>-4.688811208928286</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9010323795846804</v>
+        <v>0.8034146088957763</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.0356820430547366</v>
+        <v>-0.07988107431237207</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.78083184501633</v>
+        <v>2.631366872193415</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.693923252896882</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.849871212001835</v>
+        <v>-4.78655175355326</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8765638978507342</v>
+        <v>0.7789461271618303</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05157132118771679</v>
+        <v>-0.09577035244535226</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.785926014252586</v>
+        <v>2.636461041429671</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.692459233721553</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.026208972124764</v>
+        <v>-4.962889513676189</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8045647746262343</v>
+        <v>0.7069470039373302</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2279090813106462</v>
+        <v>-0.2721081125682817</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.6786593390035</v>
+        <v>2.529194366180584</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.690950851761482</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.954662649347887</v>
+        <v>-4.891343190899312</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8316749217769135</v>
+        <v>0.7340571510880096</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2279090813106462</v>
+        <v>-0.2721081125682817</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.677150957043428</v>
+        <v>2.527685984220513</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.690813719196918</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.910289517709319</v>
+        <v>-4.846970059260744</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8492870418677771</v>
+        <v>0.7516692711788733</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1835359496720776</v>
+        <v>-0.2277349809297131</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.703637703462006</v>
+        <v>2.55417273063909</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.690813719196918</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.902335547414546</v>
+        <v>-4.839016088965971</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8524686299856861</v>
+        <v>0.754850859296782</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1835359496720776</v>
+        <v>-0.2277349809297131</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.703637703462006</v>
+        <v>2.55417273063909</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.697195476224723</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.854679816853491</v>
+        <v>-4.791360358404916</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8779126792379131</v>
+        <v>0.780294908549009</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1358802191110219</v>
+        <v>-0.1800792503686574</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.738612898826444</v>
+        <v>2.589147926003528</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.702087849599447</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.726995507059194</v>
+        <v>-4.663676048610619</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9338787765303564</v>
+        <v>0.8362610058414524</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.00819590931672548</v>
+        <v>-0.05239494057436095</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.820115858077746</v>
+        <v>2.670650885254831</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.68884252207532</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.787662097461583</v>
+        <v>-4.724342639013008</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8963668128452731</v>
+        <v>0.7987490421563692</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.08989422603525915</v>
+        <v>-0.1340932572928946</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.757851540522498</v>
+        <v>2.608386567699583</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.692940224685948</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.742823695853184</v>
+        <v>-4.679504237404609</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9183998760992611</v>
+        <v>0.8207821054103572</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.08535079309038968</v>
+        <v>-0.1295498243480251</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.764675302900049</v>
+        <v>2.615210330077133</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674312</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.697101164317026</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.843582331610182</v>
+        <v>-4.780262873161607</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.88225736142754</v>
+        <v>0.7846395907386359</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1741763618173951</v>
+        <v>-0.2183753930750306</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.715540901294923</v>
+        <v>2.566075928472008</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163221</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.702980766844863</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.799379494524282</v>
+        <v>-4.736060036075707</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9058180987897373</v>
+        <v>0.8082003281008332</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1299735247314946</v>
+        <v>-0.1741725559891301</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.747942206074301</v>
+        <v>2.598477233251386</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.701390767314111</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.836358522187725</v>
+        <v>-4.77303906373915</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8894364881936077</v>
+        <v>0.7918187175047038</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.09299962294016412</v>
+        <v>-0.1371986541977996</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.768536547618347</v>
+        <v>2.619071574795431</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042142</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.752638532497151</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.856416601052565</v>
+        <v>-4.79309714260399</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.932661021830711</v>
+        <v>0.8350432511418071</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.09299962294016412</v>
+        <v>-0.1371986541977996</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.819784312801386</v>
+        <v>2.670319339978471</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078283</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.751079237091404</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.816485927874675</v>
+        <v>-4.7531664694261</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9470739956961203</v>
+        <v>0.8494562250072164</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.05306894976227378</v>
+        <v>-0.09726798101990924</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.842183421302374</v>
+        <v>2.692718448479458</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232398</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.746027465329674</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.77601558031197</v>
+        <v>-4.712696121863395</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9582103629594723</v>
+        <v>0.8605925922705684</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.01259860219956882</v>
+        <v>-0.05679763345720429</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.861413858078266</v>
+        <v>2.711948885255351</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162114</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.763214869422379</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.710791399184765</v>
+        <v>-4.64747194073619</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.001487439503059</v>
+        <v>0.9038696688141554</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.05262557892763681</v>
+        <v>0.008426547670001339</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.917735770847295</v>
+        <v>2.76827079802438</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639819</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.759175841721659</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.761285689541821</v>
+        <v>-4.697966231093246</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9772506956595173</v>
+        <v>0.8796329249706134</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.007604841801562567</v>
+        <v>-0.0365941894560729</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.886684300870931</v>
+        <v>2.737219328048015</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.760432634052899</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.781397345576529</v>
+        <v>-4.718077887127954</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9704628255768744</v>
+        <v>0.8728450548879703</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.01863218679898176</v>
+        <v>-0.0255668444586537</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.894557500200623</v>
+        <v>2.745092527377707</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>2.92099040507411</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.879077924849176</v>
+        <v>-4.815758466400601</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.091948364889026</v>
+        <v>0.9943305942001226</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.09207100854120703</v>
+        <v>-0.1362700397988425</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.98869335401772</v>
+        <v>2.839228381194805</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.041103314291927</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.855286356243033</v>
+        <v>-4.791966897794458</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.221577901549301</v>
+        <v>1.123960130860397</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.06827943993506475</v>
+        <v>-0.1124784711927002</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.123081204399222</v>
+        <v>2.973616231576307</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.032811290305786</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.892040774804755</v>
+        <v>-4.82872131635618</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.198584110138471</v>
+        <v>1.100966339449567</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.06827943993506475</v>
+        <v>-0.1124784711927002</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.114789180413081</v>
+        <v>2.965324207590166</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803426852654188</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.031004485889566</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.887706471747707</v>
+        <v>-4.824387013299132</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.19851102694507</v>
+        <v>1.100893256256166</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.08337066338413918</v>
+        <v>0.03917163212650371</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.203972437988384</v>
+        <v>3.054507465165468</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.563707177477392</v>
+        <v>3.7963850211787</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.048558891616357</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.878814010354424</v>
+        <v>-4.965609356603477</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.219622417229174</v>
+        <v>1.061958724661219</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.08337066338413918</v>
+        <v>0.03917163212650371</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.221526843715175</v>
+        <v>3.072061870892259</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240615.xlsx
+++ b/tame_output/ON/bt/strategyON_20240615.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-10.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>106.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-693.3%</t>
+          <t>-692.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>448.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-658.1%</t>
+          <t>-653.6%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,31 +1131,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.7%</t>
+          <t>-277.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-270.0%</t>
+          <t>-255.9%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.7%</t>
+          <t>-160.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-220.1%</t>
+          <t>-224.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
           <t>44.6%</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>44.0%</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.8%</t>
+          <t>-146.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1995"/>
+  <dimension ref="A1:G1996"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5976218536861235</v>
+        <v>-0.5908024501953608</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.887075553749589</v>
+        <v>2.889803315145894</v>
       </c>
       <c r="F1843" t="n">
         <v>1.455613419548912</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6793937541138753</v>
+        <v>-0.6725743506231125</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.844449519533726</v>
+        <v>2.847177280930031</v>
       </c>
       <c r="F1844" t="n">
         <v>1.482648992955049</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.746602861985753</v>
+        <v>-0.7397834584949903</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.822331193218677</v>
+        <v>2.825058954614982</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9541686463773649</v>
+        <v>-0.9473492428866022</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.737129675581273</v>
+        <v>2.739857436977578</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.371922669924202</v>
+        <v>-1.365103266433439</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.567954957667602</v>
+        <v>2.570682719063906</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.662054336529633</v>
+        <v>-1.65523493303887</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.451768507624351</v>
+        <v>2.454496269020656</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8814109797567796</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.870058394882711</v>
+        <v>-1.863238991391948</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.373459028837045</v>
+        <v>2.37618679023335</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8814109797567796</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.081470815770686</v>
+        <v>-2.074651412279923</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.283975516819843</v>
+        <v>2.286703278216148</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6699985588688046</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.447539542915339</v>
+        <v>-2.440720139424576</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.130632325268431</v>
+        <v>2.133360086664736</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3039298317241519</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.656030324367023</v>
+        <v>-2.649210920876261</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.067574302426525</v>
+        <v>2.07030206382283</v>
       </c>
       <c r="F1852" t="n">
         <v>0.09543905027246746</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.903231509132245</v>
+        <v>-2.896412105641482</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.976792578929005</v>
+        <v>1.97952034032531</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1155924037712799</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.395616537156342</v>
+        <v>-3.388797133665579</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.780944959763099</v>
+        <v>1.783672721159404</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3767926242528168</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.780796928086414</v>
+        <v>-3.773977524595651</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.625415342203933</v>
+        <v>1.628143103600238</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.124479701313077</v>
+        <v>-4.117660297822314</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.489711356367884</v>
+        <v>1.492439117764189</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.330991478200098</v>
+        <v>-4.324172074709336</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.403212704269333</v>
+        <v>1.405940465665638</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.6503355532806</v>
+        <v>-4.643516149789837</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.277248000937392</v>
+        <v>1.279975762333697</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.082141346430388</v>
+        <v>-5.075321942939625</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.090858571144881</v>
+        <v>1.093586332541187</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.31683534056294</v>
+        <v>-5.310015937072177</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9852657484939513</v>
+        <v>0.9879935098902566</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.652497987793392</v>
+        <v>-5.64567858430263</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8495812812577355</v>
+        <v>0.8523090426540407</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.016124232693706</v>
+        <v>-6.009304829202943</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7106183435318516</v>
+        <v>0.7133461049281569</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.381251615332452</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5638219054821842</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.789840392513131</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3991479386246719</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.066416492828964</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2837029309697994</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.482808367115961</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1151402318638777</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.753574456208606</v>
+        <v>-7.746755052717844</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01709248689549892</v>
+        <v>0.01982024829180373</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.099449278193415</v>
+        <v>-8.092629874702652</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1251578767527293</v>
+        <v>-0.1224301153564245</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.263029156377799</v>
+        <v>-8.256209752887036</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1921849079714821</v>
+        <v>-0.1894571465751773</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.559690498187997</v>
+        <v>-8.552871094697235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3070704687663532</v>
+        <v>-0.3043427073700484</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.7464102064973</v>
+        <v>-8.739590803006537</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3857846566244776</v>
+        <v>-0.3830568952281723</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.129411595239931</v>
+        <v>-9.122592191749169</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.539087313443114</v>
+        <v>-0.5363595520468092</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.311281386224966</v>
+        <v>-9.304461982734203</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.609263713865698</v>
+        <v>-0.6065359524693927</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.670811708728968</v>
+        <v>-9.663992305238205</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7477255395692484</v>
+        <v>-0.7449977781729431</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.72116077218319</v>
+        <v>-9.714341368692427</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7599491449937594</v>
+        <v>-0.7572213835974546</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.818780049604586</v>
+        <v>-9.811960646113823</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7959551053405494</v>
+        <v>-0.7932273439442441</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.966306137610228</v>
+        <v>-9.959486734119466</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8520719842212343</v>
+        <v>-0.8493442228249291</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.17056431294009</v>
+        <v>-10.16374490944933</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9282620572345373</v>
+        <v>-0.925534295838232</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.24489728920026</v>
+        <v>-10.23807788570949</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9535126932541673</v>
+        <v>-0.9507849318578621</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.442858704874723</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.17142745753281</v>
+        <v>-10.16460805404204</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9087530590937662</v>
+        <v>-0.906025297697461</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.369388873207274</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.34655187491935</v>
+        <v>-10.33973247142859</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9642476053008666</v>
+        <v>-0.9615198439045614</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.544513290593818</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.58100396893384</v>
+        <v>-10.57418456544308</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.065247607808259</v>
+        <v>-1.062519846411953</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.544513290593818</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.68537869996029</v>
+        <v>-10.67855929646952</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.113669690992813</v>
+        <v>-1.110941929596508</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.648888021620264</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.75967076365823</v>
+        <v>-10.73134545206985</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.142270726633432</v>
+        <v>-1.130940601998082</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.788762539460297</v>
+        <v>-2.744563508202661</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.488696479467427</v>
+        <v>1.515215898222009</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.88570755702652</v>
+        <v>-10.85738224543814</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.189991715351634</v>
+        <v>-1.178661590716283</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.763510916650554</v>
+        <v>-2.719311885392918</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.506541181782387</v>
+        <v>1.533060600536969</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.8336920430577</v>
+        <v>-10.80536673146933</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.165195174077708</v>
+        <v>-1.153865049442357</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.763510916650554</v>
+        <v>-2.719311885392918</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.510531517468788</v>
+        <v>1.53705093622337</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.97536388478182</v>
+        <v>-10.94703857319345</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.223339137666097</v>
+        <v>-1.212009013030747</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.763510916650554</v>
+        <v>-2.719311885392918</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.509056290570047</v>
+        <v>1.535575709324628</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.92577304035699</v>
+        <v>-10.89744772876861</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.188449389731292</v>
+        <v>-1.177119265095941</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.71392007222572</v>
+        <v>-2.669721040968084</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.553864207389819</v>
+        <v>1.580383626144401</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.91296564735221</v>
+        <v>-10.88464033576384</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.196377566176065</v>
+        <v>-1.185047441540715</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.762775847234621</v>
+        <v>-2.718576815976986</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.511499608737796</v>
+        <v>1.538019027492377</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.6871204946328</v>
+        <v>-10.65879518304443</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.096460432052092</v>
+        <v>-1.085130307416742</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.720849171647457</v>
+        <v>-2.676650140389822</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.546234687126303</v>
+        <v>1.572754105880884</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.56254183829521</v>
+        <v>-10.53421652670684</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.045489824960997</v>
+        <v>-1.034159700325647</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.720849171647457</v>
+        <v>-2.676650140389822</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.547373831682362</v>
+        <v>1.573893250436943</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.6154371263395</v>
+        <v>-10.58711181475112</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.064014166016603</v>
+        <v>-1.052684041381253</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.715893825559011</v>
+        <v>-2.671694794301376</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.552980813497537</v>
+        <v>1.579500232252118</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.54330395105162</v>
+        <v>-10.51497863946324</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.029427191662815</v>
+        <v>-1.018097067027464</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.715893825559011</v>
+        <v>-2.671694794301376</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.558714517736173</v>
+        <v>1.585233936490755</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.47193755844197</v>
+        <v>-10.4436122468536</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.010617897012821</v>
+        <v>-0.9992877723774711</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.644527432949363</v>
+        <v>-2.600328401691728</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.591797090908097</v>
+        <v>1.618316509662678</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.2081006912379</v>
+        <v>-10.17977537964953</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9149666314441007</v>
+        <v>-0.9036365068087506</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.644527432949363</v>
+        <v>-2.600328401691728</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.58191360959519</v>
+        <v>1.608433028349771</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.940858890369503</v>
+        <v>-9.912533578781128</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.809904471596115</v>
+        <v>-0.7985743469607649</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.644527432949363</v>
+        <v>-2.600328401691728</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.580079049095816</v>
+        <v>1.606598467850397</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.842951851693012</v>
+        <v>-9.814626540104637</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7710419710989798</v>
+        <v>-0.7597118464636297</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.576541683088807</v>
+        <v>-2.532342651831171</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.620570184038689</v>
+        <v>1.64708960279327</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.818998310717054</v>
+        <v>-9.790672999128679</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7607920485631028</v>
+        <v>-0.7494619239277527</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.552588142112849</v>
+        <v>-2.508389110855214</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.635610814769757</v>
+        <v>1.662130233524338</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.554938372394258</v>
+        <v>-9.526613060805882</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6684283893957366</v>
+        <v>-0.6570982647603865</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.288528203790053</v>
+        <v>-2.244329172532418</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.780786461601682</v>
+        <v>1.807305880356264</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.84785874888942</v>
+        <v>-8.819533437301045</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3883835736541021</v>
+        <v>-0.377053449018752</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.288528203790053</v>
+        <v>-2.244329172532418</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.777999427941382</v>
+        <v>1.804518846695963</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.80767445052323</v>
+        <v>-8.779349138934855</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3719662304197846</v>
+        <v>-0.3606361057844345</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.248343905423862</v>
+        <v>-2.204144874166227</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.802453630848937</v>
+        <v>1.828973049603519</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.644274579583868</v>
+        <v>-8.615949267995493</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3072394608232831</v>
+        <v>-0.295909336187933</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.0849440344845</v>
+        <v>-2.040745003226864</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.899860374633312</v>
+        <v>1.926379793387893</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291808</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.410793357354269</v>
+        <v>-8.382468045765894</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2059225430935911</v>
+        <v>-0.194592418458241</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.851462812254901</v>
+        <v>-1.807263780997266</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.047873536808924</v>
+        <v>2.074392955563504</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.261126966346755</v>
+        <v>-8.232801654758379</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1489481970035444</v>
+        <v>-0.1376180723681943</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.758559321012365</v>
+        <v>-1.71436028975473</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.100723421241486</v>
+        <v>2.127242839996067</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.128851492715867</v>
+        <v>-8.100526181127492</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1006705208041625</v>
+        <v>-0.0893403961688124</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.626283847381479</v>
+        <v>-1.582084816123843</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.175456192167045</v>
+        <v>2.201975610921626</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.938251818042715</v>
+        <v>-7.909926506454339</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.021615590247265</v>
+        <v>-0.0102854656119149</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.435684172708326</v>
+        <v>-1.39148514145069</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.292631057658573</v>
+        <v>2.319150476413154</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.689252019359134</v>
+        <v>-7.660926707770758</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.09089067044982624</v>
+        <v>0.1022207950851763</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.435684172708326</v>
+        <v>-1.39148514145069</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.305537398882232</v>
+        <v>2.332056817636813</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.794842009132238</v>
+        <v>-7.766516697543863</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.07932125505863397</v>
+        <v>-0.06799113042328386</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.54127416248143</v>
+        <v>-1.497075131223795</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.114207475419151</v>
+        <v>2.140726894173732</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.813576911250835</v>
+        <v>-7.78525159966246</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03827087402898677</v>
+        <v>-0.02694074939363666</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.546870172141561</v>
+        <v>-1.502671140883926</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.159394211500159</v>
+        <v>2.185913630254739</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.665636869843236</v>
+        <v>-7.637311558254861</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.09897378015411462</v>
+        <v>-0.08764365551876452</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.526549256233004</v>
+        <v>-1.482350224975368</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.051707838357125</v>
+        <v>2.078227257111707</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.612667347589247</v>
+        <v>-7.584342036000872</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08649995750599704</v>
+        <v>-0.07516983287064694</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.473579733979015</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.07477556545604</v>
+        <v>2.101294984210622</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.569118940818557</v>
+        <v>-7.540793629230182</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07604120689281402</v>
+        <v>-0.06471108225746391</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.473579733979015</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.067814953360947</v>
+        <v>2.094334372115529</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.326970547364699</v>
+        <v>-7.298645235776323</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03528050486987233</v>
+        <v>0.04661062950522243</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.473579733979015</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.08227730774209</v>
+        <v>2.108796726496672</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722815</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.218711410242177</v>
+        <v>-7.190386098653802</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07311628017807603</v>
+        <v>0.08444640481342613</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.473579733979015</v>
+        <v>-1.429380702721379</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.076809428201285</v>
+        <v>2.103328846955867</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.095420275425046</v>
+        <v>-7.067094963836671</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1199308281155052</v>
+        <v>0.1312609527508553</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.350288599161884</v>
+        <v>-1.306089567904249</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.14828220310214</v>
+        <v>2.174801621856722</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.074271076521603</v>
+        <v>-7.045945764933228</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1360914859142075</v>
+        <v>0.1474216105495576</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.329139400258441</v>
+        <v>-1.284940369000806</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.168672700681532</v>
+        <v>2.195192119436113</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.830505634538159</v>
+        <v>-6.802180322949783</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.229378371054636</v>
+        <v>0.2407084956899861</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.329139400258441</v>
+        <v>-1.284940369000806</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.164453409028583</v>
+        <v>2.190972827783164</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.728742814260864</v>
+        <v>-6.700417502672488</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2722078130855698</v>
+        <v>0.28353793772092</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.315920331866012</v>
+        <v>-1.271721300608377</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.174509163984056</v>
+        <v>2.201028582738637</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279181</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.478892420311789</v>
+        <v>-6.450567108723414</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3648900456489019</v>
+        <v>0.376220170284252</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.315920331866012</v>
+        <v>-1.271721300608377</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.167251238967758</v>
+        <v>2.193770657722339</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.303000327844357</v>
+        <v>-6.274675016255982</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4388460061565236</v>
+        <v>0.4501761307918737</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.315920331866012</v>
+        <v>-1.271721300608377</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.170850362488407</v>
+        <v>2.197369781242988</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.131553864821893</v>
+        <v>-6.103228553233518</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5207520974200626</v>
+        <v>0.5320822220554127</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.144473868843549</v>
+        <v>-1.100274837585914</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.287045746356438</v>
+        <v>2.31356516511102</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.906520865153071</v>
+        <v>-5.878195553564695</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6097857749038886</v>
+        <v>0.6211158995392387</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9194408691747263</v>
+        <v>-0.8752418379170909</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.421086023774029</v>
+        <v>2.44760544252861</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.842885122919136</v>
+        <v>-5.814559811330761</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.63993487285178</v>
+        <v>0.6512649974871301</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8558051269407918</v>
+        <v>-0.8116060956831563</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.463962270168707</v>
+        <v>2.490481688923288</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.799122941613295</v>
+        <v>-5.770797630024919</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6386340041579119</v>
+        <v>0.649964128793262</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8558051269407918</v>
+        <v>-0.8116060956831563</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.445156528952503</v>
+        <v>2.471675947707084</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.558692444808434</v>
+        <v>-5.530367133220059</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7365492795047337</v>
+        <v>0.7478794041400838</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6153746301359315</v>
+        <v>-0.5711755988782961</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.591157903660296</v>
+        <v>2.617677322414877</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.48644987663724</v>
+        <v>-5.458124565048864</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7693756206080318</v>
+        <v>0.7807057452433819</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6153746301359315</v>
+        <v>-0.5711755988782961</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.595087217495116</v>
+        <v>2.621606636249697</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.433451554355852</v>
+        <v>-5.405126242767476</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7912535334379269</v>
+        <v>0.802583658073277</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5600383711339927</v>
+        <v>-0.5158393398763572</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.628967556813619</v>
+        <v>2.655486975568201</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.324646668876125</v>
+        <v>-5.296321357287749</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.831773558849811</v>
+        <v>0.8431036834851611</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5600383711339927</v>
+        <v>-0.5158393398763572</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.625965628033613</v>
+        <v>2.652485046788194</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.104625870839114</v>
+        <v>-5.076300559250739</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9213609150752293</v>
+        <v>0.9326910397105794</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4188185260660124</v>
+        <v>-0.374619494808377</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.712276572085015</v>
+        <v>2.738795990839597</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.971758181775837</v>
+        <v>-4.943432870187461</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9904021735023638</v>
+        <v>1.001732298137714</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4188185260660124</v>
+        <v>-0.374619494808377</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.728170754886838</v>
+        <v>2.75469017364142</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.851585098411338</v>
+        <v>-4.823259786822963</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.039617251288465</v>
+        <v>1.050947375923815</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2986454427015135</v>
+        <v>-0.254446411443878</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.80142044934584</v>
+        <v>2.827939868100421</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.7069129533116</v>
+        <v>-4.678587641723225</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.1075742118898</v>
+        <v>1.11890433652515</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1539732976017761</v>
+        <v>-0.1097742663441406</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.898311838967122</v>
+        <v>2.924831257721703</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.766787780669293</v>
+        <v>-4.738462469080917</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.069661772348149</v>
+        <v>1.080991896983499</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2138481249594682</v>
+        <v>-0.1696490937018327</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.848424433953933</v>
+        <v>2.874943852708514</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.679988282890283</v>
+        <v>-4.651662971301908</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.126782064782319</v>
+        <v>1.138112189417669</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2138481249594682</v>
+        <v>-0.1696490937018327</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.870824927276499</v>
+        <v>2.89734434603108</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.682457989352089</v>
+        <v>-4.654132677763714</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.125866583571008</v>
+        <v>1.137196708206359</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2163178314212744</v>
+        <v>-0.1721188001636389</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.869415504772827</v>
+        <v>2.895934923527408</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.7508281756761</v>
+        <v>-4.722502864087724</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.109525431516106</v>
+        <v>1.120855556151457</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2070421323850594</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.885987846669258</v>
+        <v>2.91250726542384</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.859366356592234</v>
+        <v>-4.831041045003858</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.056546867781544</v>
+        <v>1.067876992416894</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2070421323850594</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.87642455530115</v>
+        <v>2.902943974055731</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.890359515920939</v>
+        <v>-4.862034204332564</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8688591690904488</v>
+        <v>0.8801892937257989</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2070421323850594</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.701134120341536</v>
+        <v>2.727653539096118</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.71488525612847</v>
+        <v>-4.686559944540095</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.943616104999224</v>
+        <v>0.9549462296345741</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2070421323850594</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.705701352333324</v>
+        <v>2.732220771087905</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.825821508769719</v>
+        <v>-4.797496197181344</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8749836327039315</v>
+        <v>0.8863137573392816</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2070421323850594</v>
+        <v>-0.162843101127424</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.681443381094531</v>
+        <v>2.707962799849112</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.834103582914778</v>
+        <v>-4.805778271326402</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8748021882658137</v>
+        <v>0.8861323129011638</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2153242065301178</v>
+        <v>-0.1711251752724823</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.679605521827402</v>
+        <v>2.706124940581983</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.774250963711054</v>
+        <v>-4.745925652122679</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9089156223794355</v>
+        <v>0.9202457470147856</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2153242065301178</v>
+        <v>-0.1711251752724823</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.689777908259534</v>
+        <v>2.716297327014115</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.688007500684677</v>
+        <v>-4.659682189096301</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9383592781638468</v>
+        <v>0.9496894027991969</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2153242065301178</v>
+        <v>-0.1711251752724823</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.684724178833394</v>
+        <v>2.711243597587976</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.733314320083656</v>
+        <v>-4.704989008495281</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9120123258487804</v>
+        <v>0.9233424504841306</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2561343695393486</v>
+        <v>-0.2119353382817131</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.652013856472381</v>
+        <v>2.678533275226963</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.762347424785958</v>
+        <v>-4.734022113197582</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9009509570009615</v>
+        <v>0.9122810816363116</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2561343695393486</v>
+        <v>-0.2119353382817131</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.652565729505483</v>
+        <v>2.679085148260064</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.669536943335098</v>
+        <v>-4.641211631746723</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.867347841472671</v>
+        <v>0.8786779661080211</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1633238880884892</v>
+        <v>-0.1191248568308538</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.637524710267364</v>
+        <v>2.664044129021946</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.713926412664526</v>
+        <v>-4.68560110107615</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8514655296655009</v>
+        <v>0.862795654300851</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2077133574179169</v>
+        <v>-0.1635143261602814</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.612764504594308</v>
+        <v>2.63928392334889</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.601255194428275</v>
+        <v>-4.673084828893976</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8916097254717239</v>
+        <v>0.8628778716854437</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.09504213918166671</v>
+        <v>-0.1509980539781072</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.675442944047782</v>
+        <v>2.641869395169917</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.488878193245602</v>
+        <v>-4.560707827711303</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9420518217754603</v>
+        <v>0.9133199679891801</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.09504213918166671</v>
+        <v>-0.1509980539781072</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.680934239878449</v>
+        <v>2.647360691000585</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.687112762132333</v>
+        <v>-4.758942396598034</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.874255195989307</v>
+        <v>0.8455233422030268</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2932767080683973</v>
+        <v>-0.3492326228648377</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.57349070031495</v>
+        <v>2.539917151437085</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.770114043157612</v>
+        <v>-4.841943677623313</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6794104035798487</v>
+        <v>0.6506785497935685</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.311847592595571</v>
+        <v>-0.3678035073920115</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.400703889599299</v>
+        <v>2.367130340721434</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.878728121600943</v>
+        <v>-4.950557756066644</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.756114432921722</v>
+        <v>0.7273825791354418</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.311847592595571</v>
+        <v>-0.3678035073920115</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.520853550318504</v>
+        <v>2.48728000144064</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.965326704582046</v>
+        <v>-5.037156339047747</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7359880258316038</v>
+        <v>0.7072561720453234</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.311847592595571</v>
+        <v>-0.3678035073920115</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.535366576420827</v>
+        <v>2.501793027542963</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.926943042023895</v>
+        <v>-4.998772676489596</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7487609321972328</v>
+        <v>0.7200290784109526</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2734639300374199</v>
+        <v>-0.3294198448338603</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.555816215298087</v>
+        <v>2.522242666420222</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.749826711988729</v>
+        <v>-4.82165634645443</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8163364930566013</v>
+        <v>0.7876046392703211</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2734639300374199</v>
+        <v>-0.3294198448338603</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.552545244143388</v>
+        <v>2.518971695265524</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.794918956822275</v>
+        <v>-4.866748591287975</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7989829868850959</v>
+        <v>0.7702511330988158</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3353599732068097</v>
+        <v>-0.3913158880032501</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.516091010003668</v>
+        <v>2.482517461125803</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.615543535583507</v>
+        <v>-4.687373170049208</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8645201306870174</v>
+        <v>0.8357882769007372</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.178583215036091</v>
+        <v>-0.2345391298325314</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.603944040212513</v>
+        <v>2.570370491334649</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.660557749104113</v>
+        <v>-4.732387383569813</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8273219006103649</v>
+        <v>0.7985900468240847</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2089321103506956</v>
+        <v>-0.2648880251471361</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.56654215835534</v>
+        <v>2.532968609477476</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.927562259376548</v>
+        <v>-4.999391893842248</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7262116588403367</v>
+        <v>0.6974798050540565</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4032951483936442</v>
+        <v>-0.4592510631900846</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.455615897868517</v>
+        <v>2.422042348990653</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.028760040813721</v>
+        <v>-5.100589675279421</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6849364681619692</v>
+        <v>0.6562046143756888</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4717039619389634</v>
+        <v>-0.5276598767354038</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.413774531637827</v>
+        <v>2.380200982759963</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.996284454642948</v>
+        <v>-5.068114089108649</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6955266641845945</v>
+        <v>0.6667948103983146</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4717039619389634</v>
+        <v>-0.5276598767354038</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.411374493192143</v>
+        <v>2.377800944314279</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.977246326935651</v>
+        <v>-5.049075961401352</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6996666344757585</v>
+        <v>0.6709347806894783</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5298875732701579</v>
+        <v>-0.5858434880665984</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.372989045601672</v>
+        <v>2.339415496723807</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.745557904434113</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.975284103488473</v>
+        <v>-5.08020259255197</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7550878387249762</v>
+        <v>0.8360659971679114</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5298875732701579</v>
+        <v>-0.5858434880665984</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.427625360472018</v>
+        <v>2.516997365662488</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.746391233420246</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.027604484089265</v>
+        <v>-5.132522973152762</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7349930154707929</v>
+        <v>0.8159711739137281</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4949407132612857</v>
+        <v>-0.5508966280577262</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.449426805463475</v>
+        <v>2.538798810653945</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.752399763817172</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.047861782618223</v>
+        <v>-5.15278027168172</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7328986264561359</v>
+        <v>0.8138767848990711</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4949407132612857</v>
+        <v>-0.5508966280577262</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.455435335860401</v>
+        <v>2.544807341050871</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.831552411609194</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.90011881238322</v>
+        <v>-5.005037301446717</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8711484623421588</v>
+        <v>0.952126620785094</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3271333560264026</v>
+        <v>-0.3830892708228431</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.635272397993353</v>
+        <v>2.724644403183822</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.834346033140675</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.002133494914442</v>
+        <v>-5.107051983977938</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8331362108611513</v>
+        <v>0.9141143693040865</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3271333560264026</v>
+        <v>-0.3830892708228431</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.638066019524834</v>
+        <v>2.727438024715303</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.835008381532333</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.995980788861657</v>
+        <v>-5.100899277925154</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8362596416739234</v>
+        <v>0.9172378001168586</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3209806499736183</v>
+        <v>-0.3769365647700588</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.642419991548163</v>
+        <v>2.731791996738632</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.834088858272444</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.012790087012159</v>
+        <v>-5.117708576075656</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8286163991538329</v>
+        <v>0.9095945575967681</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3377899481241199</v>
+        <v>-0.3937458629205604</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.631414889397972</v>
+        <v>2.720786894588442</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.900424412069265</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.950492088236037</v>
+        <v>-5.055410577299534</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9198711524611025</v>
+        <v>1.000849310904038</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3377899481241199</v>
+        <v>-0.3767421284188805</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.697750443194793</v>
+        <v>2.79732468908627</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.609005284458663</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.748701890570879</v>
+        <v>-4.853620379634376</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7091681039165638</v>
+        <v>0.790146262359499</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1397717559549655</v>
+        <v>-0.1787239362497261</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.525142230885684</v>
+        <v>2.624716476777161</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.679295516780838</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.688811208928286</v>
+        <v>-4.793729697991783</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8034146088957763</v>
+        <v>0.8843927673387115</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.07988107431237207</v>
+        <v>-0.1188332546071326</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.631366872193415</v>
+        <v>2.730941118084893</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.693923252896882</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.78655175355326</v>
+        <v>-4.891470242616757</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7789461271618303</v>
+        <v>0.8599242856047655</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.09577035244535226</v>
+        <v>-0.1347225327401128</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.636461041429671</v>
+        <v>2.736035287321148</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.692459233721553</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.962889513676189</v>
+        <v>-5.067808002739686</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7069470039373302</v>
+        <v>0.7879251623802652</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2721081125682817</v>
+        <v>-0.3110602928630422</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.529194366180584</v>
+        <v>2.628768612072062</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.690950851761482</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.891343190899312</v>
+        <v>-4.996261679962809</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7340571510880096</v>
+        <v>0.8150353095309448</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2721081125682817</v>
+        <v>-0.3110602928630422</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.527685984220513</v>
+        <v>2.627260230111991</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.690813719196918</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.846970059260744</v>
+        <v>-4.951888548324241</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7516692711788733</v>
+        <v>0.8326474296218085</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2277349809297131</v>
+        <v>-0.2666871612244736</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.55417273063909</v>
+        <v>2.653746976530568</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.690813719196918</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.839016088965971</v>
+        <v>-4.943934578029468</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.754850859296782</v>
+        <v>0.8358290177397172</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2277349809297131</v>
+        <v>-0.2666871612244736</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.55417273063909</v>
+        <v>2.653746976530568</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.697195476224723</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.791360358404916</v>
+        <v>-4.896278847468412</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.780294908549009</v>
+        <v>0.8612730669919442</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1800792503686574</v>
+        <v>-0.219031430663418</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.589147926003528</v>
+        <v>2.688722171895006</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.702087849599447</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.663676048610619</v>
+        <v>-4.768594537674116</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8362610058414524</v>
+        <v>0.9172391642843876</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.05239494057436095</v>
+        <v>-0.0913471208691215</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.670650885254831</v>
+        <v>2.770225131146309</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.68884252207532</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.724342639013008</v>
+        <v>-4.829261128076505</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7987490421563692</v>
+        <v>0.8797272005993044</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1340932572928946</v>
+        <v>-0.1730454375876552</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.608386567699583</v>
+        <v>2.707960813591061</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.692940224685948</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.679504237404609</v>
+        <v>-4.784422726468106</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8207821054103572</v>
+        <v>0.9017602638532924</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1295498243480251</v>
+        <v>-0.1685020046427857</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.615210330077133</v>
+        <v>2.714784575968611</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674312</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.697101164317026</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.780262873161607</v>
+        <v>-4.885181362225104</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7846395907386359</v>
+        <v>0.8656177491815711</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2183753930750306</v>
+        <v>-0.2573275733697911</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.566075928472008</v>
+        <v>2.665650174363486</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163221</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.702980766844863</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.736060036075707</v>
+        <v>-4.840978525139204</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8082003281008332</v>
+        <v>0.8891784865437684</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1741725559891301</v>
+        <v>-0.2131247362838907</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.598477233251386</v>
+        <v>2.698051479142863</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022906</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.701390767314111</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.77303906373915</v>
+        <v>-4.877957552802647</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7918187175047038</v>
+        <v>0.872796875947639</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1371986541977996</v>
+        <v>-0.1761508344925601</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.619071574795431</v>
+        <v>2.718645820686909</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042142</v>
+        <v>3.86392411404214</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.752638532497151</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.79309714260399</v>
+        <v>-4.898015631667487</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8350432511418071</v>
+        <v>0.9160214095847423</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1371986541977996</v>
+        <v>-0.1761508344925601</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.670319339978471</v>
+        <v>2.769893585869949</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078283</v>
+        <v>3.865367715078281</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.751079237091404</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.7531664694261</v>
+        <v>-4.858084958489597</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8494562250072164</v>
+        <v>0.9304343834501516</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.09726798101990924</v>
+        <v>-0.1362201613146698</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.692718448479458</v>
+        <v>2.792292694370936</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.746027465329674</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.712696121863395</v>
+        <v>-4.817614610926892</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.8605925922705684</v>
+        <v>0.9415707507135036</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.05679763345720429</v>
+        <v>-0.09574981375196484</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.711948885255351</v>
+        <v>2.811523131146829</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162114</v>
+        <v>3.842576394162112</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.763214869422379</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.64747194073619</v>
+        <v>-4.752390429799687</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9038696688141554</v>
+        <v>0.9848478272570906</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.008426547670001339</v>
+        <v>-0.03052563262475921</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.76827079802438</v>
+        <v>2.867845043915857</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639819</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.759175841721659</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.697966231093246</v>
+        <v>-4.802884720156743</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8796329249706134</v>
+        <v>0.9606110834135486</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.0365941894560729</v>
+        <v>-0.07554636975083345</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.737219328048015</v>
+        <v>2.836793573939493</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.760432634052899</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.718077887127954</v>
+        <v>-4.822996376191451</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.8728450548879703</v>
+        <v>0.9538232133309055</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.0255668444586537</v>
+        <v>-0.06451902475341426</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.745092527377707</v>
+        <v>2.844666773269185</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.92099040507411</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.815758466400601</v>
+        <v>-4.920676955464097</v>
       </c>
       <c r="E1991" t="n">
-        <v>0.9943305942001226</v>
+        <v>1.075308752643058</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.1362700397988425</v>
+        <v>-0.1752222200936031</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.839228381194805</v>
+        <v>2.938802627086282</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.041103314291927</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.791966897794458</v>
+        <v>-4.896885386857955</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.123960130860397</v>
+        <v>1.204938289303332</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.1124784711927002</v>
+        <v>-0.1514306514874608</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.973616231576307</v>
+        <v>3.073190477467785</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756014</v>
+        <v>3.814259761756012</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.032811290305786</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.82872131635618</v>
+        <v>-4.933639805419677</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.100966339449567</v>
+        <v>1.181944497892502</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.1124784711927002</v>
+        <v>-0.1514306514874608</v>
       </c>
       <c r="G1993" t="n">
-        <v>2.965324207590166</v>
+        <v>3.064898453481644</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654188</v>
+        <v>3.803426852654186</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.031004485889566</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.824387013299132</v>
+        <v>-4.929305502362629</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.100893256256166</v>
+        <v>1.181871414699101</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.03917163212650371</v>
+        <v>0.000219451831743156</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.054507465165468</v>
+        <v>3.154081711056946</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,45 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.7963850211787</v>
+        <v>3.796293177717113</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.048558891616357</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.965609356603477</v>
+        <v>-4.920413040969346</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.061958724661219</v>
+        <v>1.202982804983205</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.03917163212650371</v>
+        <v>0.000219451831743156</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.072061870892259</v>
+        <v>3.171636116783737</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="2" t="n">
+        <v>45458</v>
+      </c>
+      <c r="B1996" t="n">
+        <v>3.426045575070461</v>
+      </c>
+      <c r="C1996" t="n">
+        <v>3.007340798623166</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>-4.920413040969346</v>
+      </c>
+      <c r="E1996" t="n">
+        <v>1.202982804983205</v>
+      </c>
+      <c r="F1996" t="n">
+        <v>0.000219451831743156</v>
+      </c>
+      <c r="G1996" t="n">
+        <v>3.000404595609534</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240615.xlsx
+++ b/tame_output/ON/bt/strategyON_20240615.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>15.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.8%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>125.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.4%</t>
+          <t>454.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-653.6%</t>
+          <t>-627.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-255.9%</t>
+          <t>-245.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.6%</t>
+          <t>305.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-224.0%</t>
+          <t>-202.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-146.0%</t>
+          <t>-120.0%</t>
         </is>
       </c>
     </row>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722815</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.673084828893976</v>
+        <v>-4.5729298828399</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8628778716854437</v>
+        <v>0.902939850107074</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1509980539781072</v>
+        <v>-0.05084310792403124</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.641869395169917</v>
+        <v>2.701962362802363</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.560707827711303</v>
+        <v>-4.460552881657227</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9133199679891801</v>
+        <v>0.9533819464108104</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1509980539781072</v>
+        <v>-0.05084310792403124</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.647360691000585</v>
+        <v>2.70745365863303</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.758942396598034</v>
+        <v>-4.658787450543958</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8455233422030268</v>
+        <v>0.8855853206246571</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3492326228648377</v>
+        <v>-0.2490776768107618</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.539917151437085</v>
+        <v>2.600010119069531</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.841943677623313</v>
+        <v>-4.741788731569237</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6506785497935685</v>
+        <v>0.6907405282151988</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3678035073920115</v>
+        <v>-0.2676485613379356</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.367130340721434</v>
+        <v>2.42722330835388</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.950557756066644</v>
+        <v>-4.850402810012568</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7273825791354418</v>
+        <v>0.7674445575570721</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3678035073920115</v>
+        <v>-0.2676485613379356</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.48728000144064</v>
+        <v>2.547372969073086</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.037156339047747</v>
+        <v>-4.937001392993671</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7072561720453234</v>
+        <v>0.7473181504669539</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3678035073920115</v>
+        <v>-0.2676485613379356</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.501793027542963</v>
+        <v>2.561885995175408</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.998772676489596</v>
+        <v>-4.89861773043552</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7200290784109526</v>
+        <v>0.7600910568325829</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3294198448338603</v>
+        <v>-0.2292648987797844</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.522242666420222</v>
+        <v>2.582335634052668</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.82165634645443</v>
+        <v>-4.721501400400354</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7876046392703211</v>
+        <v>0.8276666176919514</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3294198448338603</v>
+        <v>-0.2292648987797844</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.518971695265524</v>
+        <v>2.57906466289797</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.866748591287975</v>
+        <v>-4.7665936452339</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7702511330988158</v>
+        <v>0.810313111520446</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3913158880032501</v>
+        <v>-0.2911609419491742</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.482517461125803</v>
+        <v>2.542610428758249</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.687373170049208</v>
+        <v>-4.587218223995132</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8357882769007372</v>
+        <v>0.8758502553223675</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2345391298325314</v>
+        <v>-0.1343841837784555</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.570370491334649</v>
+        <v>2.630463458967094</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.732387383569813</v>
+        <v>-4.632232437515738</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7985900468240847</v>
+        <v>0.838652025245715</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2648880251471361</v>
+        <v>-0.1647330790930601</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.532968609477476</v>
+        <v>2.593061577109922</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.999391893842248</v>
+        <v>-4.899236947788173</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6974798050540565</v>
+        <v>0.7375417834756868</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4592510631900846</v>
+        <v>-0.3590961171360087</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.422042348990653</v>
+        <v>2.482135316623098</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.100589675279421</v>
+        <v>-5.000434729225345</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6562046143756888</v>
+        <v>0.6962665927973191</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5276598767354038</v>
+        <v>-0.4275049306813279</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.380200982759963</v>
+        <v>2.440293950392408</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.068114089108649</v>
+        <v>-4.967959143054573</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6667948103983146</v>
+        <v>0.7068567888199446</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5276598767354038</v>
+        <v>-0.4275049306813279</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.377800944314279</v>
+        <v>2.437893911946725</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.049075961401352</v>
+        <v>-4.948921015347276</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6709347806894783</v>
+        <v>0.7109967591111086</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5858434880665984</v>
+        <v>-0.4856885420125224</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.339415496723807</v>
+        <v>2.399508464356253</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.08020259255197</v>
+        <v>-4.980047646497894</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8360659971679114</v>
+        <v>0.8761279755895417</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5858434880665984</v>
+        <v>-0.4856885420125224</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.516997365662488</v>
+        <v>2.577090333294934</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.132522973152762</v>
+        <v>-5.032368027098686</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8159711739137281</v>
+        <v>0.8560331523353586</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5508966280577262</v>
+        <v>-0.4507416820036503</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.538798810653945</v>
+        <v>2.598891778286391</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.15278027168172</v>
+        <v>-5.052625325627644</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8138767848990711</v>
+        <v>0.8539387633207012</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5508966280577262</v>
+        <v>-0.4507416820036503</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.544807341050871</v>
+        <v>2.604900308683316</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.005037301446717</v>
+        <v>-4.904882355392641</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.952126620785094</v>
+        <v>0.9921885992067243</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3830892708228431</v>
+        <v>-0.2829343247687671</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.724644403183822</v>
+        <v>2.784737370816268</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.107051983977938</v>
+        <v>-5.006897037923863</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9141143693040865</v>
+        <v>0.9541763477257168</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3830892708228431</v>
+        <v>-0.2829343247687671</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.727438024715303</v>
+        <v>2.787530992347749</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.100899277925154</v>
+        <v>-5.000744331871078</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9172378001168586</v>
+        <v>0.9572997785384889</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3769365647700588</v>
+        <v>-0.2767816187159828</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.731791996738632</v>
+        <v>2.791884964371078</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.117708576075656</v>
+        <v>-5.01755363002158</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9095945575967681</v>
+        <v>0.9496565360183982</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3937458629205604</v>
+        <v>-0.2935909168664845</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.720786894588442</v>
+        <v>2.780879862220887</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.055410577299534</v>
+        <v>-4.955255631245458</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.000849310904038</v>
+        <v>1.040911289325668</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3767421284188805</v>
+        <v>-0.2935909168664845</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.79732468908627</v>
+        <v>2.847215416017708</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.853620379634376</v>
+        <v>-4.7534654335803</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.790146262359499</v>
+        <v>0.8302082407811293</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1787239362497261</v>
+        <v>-0.09557272469733008</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.624716476777161</v>
+        <v>2.674607203708599</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.793729697991783</v>
+        <v>-4.693574751937707</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8843927673387115</v>
+        <v>0.9244547457603418</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1188332546071326</v>
+        <v>-0.0356820430547366</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.730941118084893</v>
+        <v>2.78083184501633</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.891470242616757</v>
+        <v>-4.791315296562681</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8599242856047655</v>
+        <v>0.8999862640263958</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1347225327401128</v>
+        <v>-0.05157132118771679</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.736035287321148</v>
+        <v>2.785926014252586</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.067808002739686</v>
+        <v>-4.96765305668561</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7879251623802652</v>
+        <v>0.8279871408018957</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3110602928630422</v>
+        <v>-0.2279090813106462</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.628768612072062</v>
+        <v>2.6786593390035</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.996261679962809</v>
+        <v>-4.896106733908733</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8150353095309448</v>
+        <v>0.8550972879525751</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3110602928630422</v>
+        <v>-0.2279090813106462</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.627260230111991</v>
+        <v>2.677150957043428</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.951888548324241</v>
+        <v>-4.851733602270165</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8326474296218085</v>
+        <v>0.8727094080434388</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2666871612244736</v>
+        <v>-0.1835359496720776</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.653746976530568</v>
+        <v>2.703637703462006</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.943934578029468</v>
+        <v>-4.843779631975393</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8358290177397172</v>
+        <v>0.8758909961613477</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2666871612244736</v>
+        <v>-0.1835359496720776</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.653746976530568</v>
+        <v>2.703637703462006</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.896278847468412</v>
+        <v>-4.796123901414337</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8612730669919442</v>
+        <v>0.9013350454135747</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.219031430663418</v>
+        <v>-0.1358802191110219</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.688722171895006</v>
+        <v>2.738612898826444</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.768594537674116</v>
+        <v>-4.66843959162004</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9172391642843876</v>
+        <v>0.9573011427060178</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.0913471208691215</v>
+        <v>-0.00819590931672548</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.770225131146309</v>
+        <v>2.820115858077746</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.829261128076505</v>
+        <v>-4.729106182022429</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8797272005993044</v>
+        <v>0.9197891790209347</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1730454375876552</v>
+        <v>-0.08989422603525915</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.707960813591061</v>
+        <v>2.757851540522498</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.784422726468106</v>
+        <v>-4.68426778041403</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9017602638532924</v>
+        <v>0.9418222422749227</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1685020046427857</v>
+        <v>-0.08535079309038968</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.714784575968611</v>
+        <v>2.764675302900049</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.885181362225104</v>
+        <v>-4.627151226876812</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8656177491815711</v>
+        <v>0.968829803320888</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2573275733697911</v>
+        <v>-0.0416235338911633</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.665650174363486</v>
+        <v>2.795072598050663</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.840978525139204</v>
+        <v>-4.582948389790912</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8891784865437684</v>
+        <v>0.9923905406830853</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2131247362838907</v>
+        <v>0.002579303194737148</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.698051479142863</v>
+        <v>2.82747390283004</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022906</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.877957552802647</v>
+        <v>-4.619927417454354</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.872796875947639</v>
+        <v>0.9760089300869559</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1761508344925601</v>
+        <v>0.03955320498606768</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.718645820686909</v>
+        <v>2.848068244374086</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86392411404214</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.898015631667487</v>
+        <v>-4.639985496319195</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9160214095847423</v>
+        <v>1.019233463724059</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1761508344925601</v>
+        <v>0.03955320498606768</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.769893585869949</v>
+        <v>2.899316009557126</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078281</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.858084958489597</v>
+        <v>-4.600054823141305</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9304343834501516</v>
+        <v>1.033646437589469</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1362201613146698</v>
+        <v>0.07948387816395802</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.792292694370936</v>
+        <v>2.921715118058113</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232397</v>
+        <v>3.864518876232398</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.817614610926892</v>
+        <v>-4.5595844755786</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9415707507135036</v>
+        <v>1.04478280485282</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.09574981375196484</v>
+        <v>0.119954225726663</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.811523131146829</v>
+        <v>2.940945554834006</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162112</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.752390429799687</v>
+        <v>-4.494360294451394</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9848478272570906</v>
+        <v>1.088059881396408</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.03052563262475921</v>
+        <v>0.1851784068538686</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.867845043915857</v>
+        <v>2.997267467603034</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.802884720156743</v>
+        <v>-4.544854584808451</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9606110834135486</v>
+        <v>1.063823137552866</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.07554636975083345</v>
+        <v>0.1401576697277944</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.836793573939493</v>
+        <v>2.96621599762667</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.822996376191451</v>
+        <v>-4.564966240843159</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9538232133309055</v>
+        <v>1.057035267470222</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.06451902475341426</v>
+        <v>0.1511850147252136</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.844666773269185</v>
+        <v>2.974089196956362</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.920676955464097</v>
+        <v>-4.662646820115805</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.075308752643058</v>
+        <v>1.178520806782375</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.1752222200936031</v>
+        <v>0.04048181938502476</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.938802627086282</v>
+        <v>3.068225050773459</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.896885386857955</v>
+        <v>-4.638855251509662</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.204938289303332</v>
+        <v>1.308150343442649</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.1514306514874608</v>
+        <v>0.06427338799116705</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.073190477467785</v>
+        <v>3.202612901154962</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756012</v>
+        <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.933639805419677</v>
+        <v>-4.675609670071385</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.181944497892502</v>
+        <v>1.285156552031819</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.1514306514874608</v>
+        <v>0.06427338799116705</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.064898453481644</v>
+        <v>3.194320877168821</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654186</v>
+        <v>3.803426852654188</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.929305502362629</v>
+        <v>-4.671275367014337</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.181871414699101</v>
+        <v>1.285083468838418</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.000219451831743156</v>
+        <v>0.215923491310371</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.154081711056946</v>
+        <v>3.283504134744123</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.920413040969346</v>
+        <v>-4.662382905621054</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.202982804983205</v>
+        <v>1.306194859122522</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.000219451831743156</v>
+        <v>0.215923491310371</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.171636116783737</v>
+        <v>3.301058540470914</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.426045575070461</v>
+        <v>3.844614030643275</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.007340798623166</v>
+        <v>3.26755252407765</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.920413040969346</v>
+        <v>-4.662382905621054</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.202982804983205</v>
+        <v>1.306194859122522</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.000219451831743156</v>
+        <v>0.215923491310371</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.000404595609534</v>
+        <v>3.260616321064017</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240615.xlsx
+++ b/tame_output/ON/bt/strategyON_20240615.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>7.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.4%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-705.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.2%</t>
+          <t>448.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-627.8%</t>
+          <t>-640.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-282.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>-651.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-245.6%</t>
+          <t>-250.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-120.0%</t>
+          <t>-127.9%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7397834584949903</v>
+        <v>-0.8678834074299461</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.825058954614982</v>
+        <v>2.773818975041</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9473492428866022</v>
+        <v>-1.075449191821558</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.739857436977578</v>
+        <v>2.688617457403596</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.365103266433439</v>
+        <v>-1.493203215368395</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.570682719063906</v>
+        <v>2.519442739489924</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.65523493303887</v>
+        <v>-1.783334881973826</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.454496269020656</v>
+        <v>2.403256289446674</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8814109797567796</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.863238991391948</v>
+        <v>-1.991338940326904</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.37618679023335</v>
+        <v>2.324946810659368</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8814109797567796</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.074651412279923</v>
+        <v>-2.202751361214879</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.286703278216148</v>
+        <v>2.235463298642166</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6699985588688046</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.440720139424576</v>
+        <v>-2.568820088359531</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.133360086664736</v>
+        <v>2.082120107090754</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3039298317241519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.649210920876261</v>
+        <v>-2.777310869811216</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.07030206382283</v>
+        <v>2.019062084248848</v>
       </c>
       <c r="F1852" t="n">
         <v>0.09543905027246746</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.896412105641482</v>
+        <v>-3.024512054576437</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.97952034032531</v>
+        <v>1.928280360751328</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1155924037712799</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.388797133665579</v>
+        <v>-3.516897082600534</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.783672721159404</v>
+        <v>1.732432741585422</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3767926242528168</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.773977524595651</v>
+        <v>-3.902077473530607</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.628143103600238</v>
+        <v>1.576903124026256</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117660297822314</v>
+        <v>-4.245760246757269</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492439117764189</v>
+        <v>1.441199138190207</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.324172074709336</v>
+        <v>-4.452272023644291</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.405940465665638</v>
+        <v>1.354700486091656</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.643516149789837</v>
+        <v>-4.771616098724793</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.279975762333697</v>
+        <v>1.228735782759715</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.075321942939625</v>
+        <v>-5.20342189187458</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.093586332541187</v>
+        <v>1.042346352967205</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.310015937072177</v>
+        <v>-5.438115886007132</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9879935098902566</v>
+        <v>0.9367535303162744</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.64567858430263</v>
+        <v>-5.773778533237585</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8523090426540407</v>
+        <v>0.8010690630800585</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.009304829202943</v>
+        <v>-6.137404778137898</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7133461049281569</v>
+        <v>0.6621061253541747</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.37443221184169</v>
+        <v>-6.502532160776645</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5665496668784895</v>
+        <v>0.5153096873045073</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.783020989022368</v>
+        <v>-6.911120937957323</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4018757000209767</v>
+        <v>0.350635720446995</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-7.187697038273155</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.2351907127921229</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.604088912560153</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.06662801368620119</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.746755052717844</v>
+        <v>-7.874855001652798</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01982024829180373</v>
+        <v>-0.03141973128217801</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.092629874702652</v>
+        <v>-8.220729823637607</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1224301153564245</v>
+        <v>-0.1736700949304062</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.256209752887036</v>
+        <v>-8.384309701821991</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1894571465751773</v>
+        <v>-0.2406971261491591</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.552871094697235</v>
+        <v>-8.680971043632189</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3043427073700484</v>
+        <v>-0.3555826869440302</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.739590803006537</v>
+        <v>-8.867690751941492</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3830568952281723</v>
+        <v>-0.4342968748021541</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.122592191749169</v>
+        <v>-9.250692140684123</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5363595520468092</v>
+        <v>-0.5875995316207909</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.304461982734203</v>
+        <v>-9.432561931669158</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6065359524693927</v>
+        <v>-0.6577759320433745</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.663992305238205</v>
+        <v>-9.792092254173159</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7449977781729431</v>
+        <v>-0.7962377577469248</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714341368692427</v>
+        <v>-9.842441317627381</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7572213835974546</v>
+        <v>-0.8084613631714364</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.811960646113823</v>
+        <v>-9.940060595048777</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7932273439442441</v>
+        <v>-0.8444673235182258</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959486734119466</v>
+        <v>-10.08758668305442</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8493442228249291</v>
+        <v>-0.9005842023989108</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141698</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16374490944933</v>
+        <v>-10.29184485838428</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.925534295838232</v>
+        <v>-0.9767742754122137</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23807788570949</v>
+        <v>-10.36617783464445</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9507849318578621</v>
+        <v>-1.002024911431844</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.442858704874723</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.16460805404204</v>
+        <v>-10.292708002977</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.906025297697461</v>
+        <v>-0.9572652772714427</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.369388873207274</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33973247142859</v>
+        <v>-10.46783242036354</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9615198439045614</v>
+        <v>-1.012759823478543</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.544513290593818</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.57418456544308</v>
+        <v>-10.70228451437803</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.062519846411953</v>
+        <v>-1.113759825985935</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.544513290593818</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.67855929646952</v>
+        <v>-10.80665924540448</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.110941929596508</v>
+        <v>-1.16218190917049</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.648888021620264</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.73134545206985</v>
+        <v>-10.85944540100481</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.130940601998082</v>
+        <v>-1.182180581572064</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.744563508202661</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.85738224543814</v>
+        <v>-10.98548219437309</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.178661590716283</v>
+        <v>-1.229901570290265</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.719311885392918</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.80536673146933</v>
+        <v>-10.93346668040428</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.153865049442357</v>
+        <v>-1.205105029016339</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.719311885392918</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.94703857319345</v>
+        <v>-11.0751385221284</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.212009013030747</v>
+        <v>-1.263248992604729</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.719311885392918</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.89744772876861</v>
+        <v>-11.02554767770357</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.177119265095941</v>
+        <v>-1.228359244669923</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.669721040968084</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.88464033576384</v>
+        <v>-11.01274028469879</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.185047441540715</v>
+        <v>-1.236287421114696</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.718576815976986</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.65879518304443</v>
+        <v>-10.78689513197938</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.085130307416742</v>
+        <v>-1.136370286990724</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.676650140389822</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.53421652670684</v>
+        <v>-10.66231647564179</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.034159700325647</v>
+        <v>-1.085399679899627</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.676650140389822</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.58711181475112</v>
+        <v>-10.71521176368608</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.052684041381253</v>
+        <v>-1.103924020955234</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.671694794301376</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.51497863946324</v>
+        <v>-10.6430785883982</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.018097067027464</v>
+        <v>-1.069337046601445</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.671694794301376</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.4436122468536</v>
+        <v>-10.57171219578855</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9992877723774711</v>
+        <v>-1.050527751951452</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.600328401691728</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17977537964953</v>
+        <v>-10.30787532858448</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9036365068087506</v>
+        <v>-0.9548764863827315</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.600328401691728</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.912533578781128</v>
+        <v>-10.04063352771608</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7985743469607649</v>
+        <v>-0.8498143265347458</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.600328401691728</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.814626540104637</v>
+        <v>-9.94272648903959</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7597118464636297</v>
+        <v>-0.8109518260376105</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.532342651831171</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.790672999128679</v>
+        <v>-9.918772948063632</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7494619239277527</v>
+        <v>-0.800701903501734</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.508389110855214</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.526613060805882</v>
+        <v>-9.654713009740835</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6570982647603865</v>
+        <v>-0.7083382443343673</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.244329172532418</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.819533437301045</v>
+        <v>-8.947633386235998</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.377053449018752</v>
+        <v>-0.4282934285927333</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.244329172532418</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.779349138934855</v>
+        <v>-8.907449087869807</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3606361057844345</v>
+        <v>-0.4118760853584158</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.204144874166227</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.615949267995493</v>
+        <v>-8.744049216930446</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.295909336187933</v>
+        <v>-0.3471493157619143</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.040745003226864</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291808</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.382468045765894</v>
+        <v>-8.510567994700846</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.194592418458241</v>
+        <v>-0.2458323980322219</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.807263780997266</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.232801654758379</v>
+        <v>-8.360901603693332</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1376180723681943</v>
+        <v>-0.1888580519421756</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.71436028975473</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.100526181127492</v>
+        <v>-8.228626130062445</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0893403961688124</v>
+        <v>-0.1405803757427937</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.582084816123843</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.909926506454339</v>
+        <v>-8.038026455389291</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0102854656119149</v>
+        <v>-0.06152544518589531</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.39148514145069</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.660926707770758</v>
+        <v>-7.78902665670571</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1022207950851763</v>
+        <v>0.05098081551119593</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.39148514145069</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.766516697543863</v>
+        <v>-7.894616646478815</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.06799113042328386</v>
+        <v>-0.1192311099972647</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.497075131223795</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.78525159966246</v>
+        <v>-7.913351548597412</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.02694074939363666</v>
+        <v>-0.07818072896761707</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.502671140883926</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.637311558254861</v>
+        <v>-7.765411507189812</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.08764365551876452</v>
+        <v>-0.1388836350927449</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.482350224975368</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.584342036000872</v>
+        <v>-7.712441984935824</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.07516983287064694</v>
+        <v>-0.1264098124446278</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.429380702721379</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.540793629230182</v>
+        <v>-7.668893578165133</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.06471108225746391</v>
+        <v>-0.1159510618314448</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.429380702721379</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.298645235776323</v>
+        <v>-7.426745184711275</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04661062950522243</v>
+        <v>-0.00462935006875842</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.429380702721379</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722815</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.190386098653802</v>
+        <v>-7.318486047588753</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.08444640481342613</v>
+        <v>0.03320642523944528</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.429380702721379</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.067094963836671</v>
+        <v>-7.195194912771623</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1312609527508553</v>
+        <v>0.0800209731768744</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.306089567904249</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.045945764933228</v>
+        <v>-7.174045713868179</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1474216105495576</v>
+        <v>0.09618163097557719</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.284940369000806</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.802180322949783</v>
+        <v>-6.930280271884735</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2407084956899861</v>
+        <v>0.1894685161160052</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.284940369000806</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.700417502672488</v>
+        <v>-6.82851745160744</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.28353793772092</v>
+        <v>0.2322979581469395</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.271721300608377</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279181</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.450567108723414</v>
+        <v>-6.578667057658365</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.376220170284252</v>
+        <v>0.3249801907102712</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.271721300608377</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.274675016255982</v>
+        <v>-6.402774965190932</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4501761307918737</v>
+        <v>0.3989361512178933</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.271721300608377</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.103228553233518</v>
+        <v>-6.231328502168469</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5320822220554127</v>
+        <v>0.4808422424814323</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.100274837585914</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.878195553564695</v>
+        <v>-6.006295502499646</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6211158995392387</v>
+        <v>0.5698759199652588</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8752418379170909</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.814559811330761</v>
+        <v>-5.942659760265712</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6512649974871301</v>
+        <v>0.6000250179131497</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8116060956831563</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.770797630024919</v>
+        <v>-5.89889757895987</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.649964128793262</v>
+        <v>0.5987241492192821</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8116060956831563</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.530367133220059</v>
+        <v>-5.65846708215501</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7478794041400838</v>
+        <v>0.6966394245661034</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5711755988782961</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.458124565048864</v>
+        <v>-5.586224513983815</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7807057452433819</v>
+        <v>0.7294657656694015</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5711755988782961</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.405126242767476</v>
+        <v>-5.533226191702427</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.802583658073277</v>
+        <v>0.7513436784992966</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5158393398763572</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.296321357287749</v>
+        <v>-5.4244213062227</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8431036834851611</v>
+        <v>0.7918637039111811</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5158393398763572</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.076300559250739</v>
+        <v>-5.20440050818569</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9326910397105794</v>
+        <v>0.8814510601365995</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.374619494808377</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.943432870187461</v>
+        <v>-5.071532819122412</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.001732298137714</v>
+        <v>0.9504923185637337</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.374619494808377</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.823259786822963</v>
+        <v>-4.951359735757913</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.050947375923815</v>
+        <v>0.9997073963498351</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.254446411443878</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.678587641723225</v>
+        <v>-4.806687590658176</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.11890433652515</v>
+        <v>1.06766435695117</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.1097742663441406</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.738462469080917</v>
+        <v>-4.866562418015868</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.080991896983499</v>
+        <v>1.029751917409519</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1696490937018327</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.651662971301908</v>
+        <v>-4.779762920236859</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.138112189417669</v>
+        <v>1.086872209843688</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1696490937018327</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.654132677763714</v>
+        <v>-4.782232626698665</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.137196708206359</v>
+        <v>1.085956728632378</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1721188001636389</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.722502864087724</v>
+        <v>-4.850602813022675</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.120855556151457</v>
+        <v>1.069615576577476</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.162843101127424</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.831041045003858</v>
+        <v>-4.959140993938809</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.067876992416894</v>
+        <v>1.016637012842914</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.162843101127424</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.862034204332564</v>
+        <v>-4.990134153267515</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8801892937257989</v>
+        <v>0.8289493141518185</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.162843101127424</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.686559944540095</v>
+        <v>-4.814659893475046</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9549462296345741</v>
+        <v>0.9037062500605939</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.162843101127424</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.797496197181344</v>
+        <v>-4.925596146116295</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8863137573392816</v>
+        <v>0.8350737777653015</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.162843101127424</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.805778271326402</v>
+        <v>-4.933878220261353</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8861323129011638</v>
+        <v>0.8348923333271836</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1711251752724823</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.745925652122679</v>
+        <v>-4.87402560105763</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9202457470147856</v>
+        <v>0.8690057674408052</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1711251752724823</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.659682189096301</v>
+        <v>-4.787782138031252</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9496894027991969</v>
+        <v>0.8984494232252165</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1711251752724823</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.704989008495281</v>
+        <v>-4.833088957430232</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9233424504841306</v>
+        <v>0.8721024709101501</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2119353382817131</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.734022113197582</v>
+        <v>-4.862122062132533</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9122810816363116</v>
+        <v>0.8610411020623312</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2119353382817131</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.641211631746723</v>
+        <v>-4.769311580681673</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8786779661080211</v>
+        <v>0.8274379865340409</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1191248568308538</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.68560110107615</v>
+        <v>-4.813701050011101</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.862795654300851</v>
+        <v>0.8115556747268706</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1635143261602814</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.5729298828399</v>
+        <v>-4.701029831774851</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.902939850107074</v>
+        <v>0.8516998705330936</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.05084310792403124</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.460552881657227</v>
+        <v>-4.588652830592178</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9533819464108104</v>
+        <v>0.90214196683683</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.05084310792403124</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.658787450543958</v>
+        <v>-4.786887399478909</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8855853206246571</v>
+        <v>0.8343453410506769</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2490776768107618</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.741788731569237</v>
+        <v>-4.869888680504188</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6907405282151988</v>
+        <v>0.6395005486412186</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2676485613379356</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.850402810012568</v>
+        <v>-4.978502758947519</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7674445575570721</v>
+        <v>0.7162045779830917</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2676485613379356</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.937001392993671</v>
+        <v>-5.065101341928622</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7473181504669539</v>
+        <v>0.6960781708929735</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2676485613379356</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.89861773043552</v>
+        <v>-5.026717679370471</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7600910568325829</v>
+        <v>0.7088510772586027</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2292648987797844</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.721501400400354</v>
+        <v>-4.849601349335305</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8276666176919514</v>
+        <v>0.776426638117971</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2292648987797844</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.7665936452339</v>
+        <v>-4.89469359416885</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.810313111520446</v>
+        <v>0.7590731319464659</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2911609419491742</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.587218223995132</v>
+        <v>-4.715318172930083</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8758502553223675</v>
+        <v>0.8246102757483873</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1343841837784555</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.632232437515738</v>
+        <v>-4.760332386450688</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.838652025245715</v>
+        <v>0.7874120456717346</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1647330790930601</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.899236947788173</v>
+        <v>-5.027336896723123</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7375417834756868</v>
+        <v>0.6863018039017064</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3590961171360087</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.000434729225345</v>
+        <v>-5.128534678160296</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6962665927973191</v>
+        <v>0.6450266132233389</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4275049306813279</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.967959143054573</v>
+        <v>-5.096059091989524</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7068567888199446</v>
+        <v>0.6556168092459642</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4275049306813279</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.948921015347276</v>
+        <v>-5.077020964282227</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7109967591111086</v>
+        <v>0.6597567795371284</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4856885420125224</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.980047646497894</v>
+        <v>-5.108147595432845</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8761279755895417</v>
+        <v>0.8248879960155615</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4856885420125224</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.032368027098686</v>
+        <v>-5.160467976033637</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8560331523353586</v>
+        <v>0.8047931727613782</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4507416820036503</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.052625325627644</v>
+        <v>-5.180725274562595</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8539387633207012</v>
+        <v>0.8026987837467212</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4507416820036503</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.904882355392641</v>
+        <v>-5.032982304327592</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9921885992067243</v>
+        <v>0.9409486196327439</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2829343247687671</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.006897037923863</v>
+        <v>-5.134996986858813</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9541763477257168</v>
+        <v>0.9029363681517366</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2829343247687671</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394733</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.000744331871078</v>
+        <v>-5.128844280806029</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9572997785384889</v>
+        <v>0.9060597989645087</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2767816187159828</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.01755363002158</v>
+        <v>-5.145653578956531</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9496565360183982</v>
+        <v>0.8984165564444182</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2935909168664845</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.955255631245458</v>
+        <v>-5.083355580180409</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.040911289325668</v>
+        <v>0.9896713097516878</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2935909168664845</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.7534654335803</v>
+        <v>-4.881565382515251</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8302082407811293</v>
+        <v>0.7789682612071491</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.09557272469733008</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.693574751937707</v>
+        <v>-4.821674700872657</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9244547457603418</v>
+        <v>0.8732147661863616</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.0356820430547366</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319551</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.791315296562681</v>
+        <v>-4.919415245497632</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8999862640263958</v>
+        <v>0.8487462844524154</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.05157132118771679</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.96765305668561</v>
+        <v>-5.095753005620561</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8279871408018957</v>
+        <v>0.7767471612279153</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2279090813106462</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.896106733908733</v>
+        <v>-5.024206682843684</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8550972879525751</v>
+        <v>0.8038573083785949</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2279090813106462</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.851733602270165</v>
+        <v>-4.979833551205116</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8727094080434388</v>
+        <v>0.8214694284694584</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1835359496720776</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863229</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.843779631975393</v>
+        <v>-4.971879580910343</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8758909961613477</v>
+        <v>0.8246510165873673</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1835359496720776</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.796123901414337</v>
+        <v>-4.924223850349287</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9013350454135747</v>
+        <v>0.8500950658395943</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1358802191110219</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326881</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.66843959162004</v>
+        <v>-4.796539540554991</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9573011427060178</v>
+        <v>0.9060611631320377</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.00819590931672548</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.729106182022429</v>
+        <v>-4.85720613095738</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9197891790209347</v>
+        <v>0.8685491994469543</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.08989422603525915</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816866067690032</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.68426778041403</v>
+        <v>-4.812367729348981</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9418222422749227</v>
+        <v>0.8905822627009423</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.08535079309038968</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674316</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.627151226876812</v>
+        <v>-4.755251175811763</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.968829803320888</v>
+        <v>0.9175898237469078</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.0416235338911633</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163225</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.582948389790912</v>
+        <v>-4.711048338725862</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9923905406830853</v>
+        <v>0.9411505611091051</v>
       </c>
       <c r="F1983" t="n">
         <v>0.002579303194737148</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.83822866302291</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.619927417454354</v>
+        <v>-4.748027366389305</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9760089300869559</v>
+        <v>0.9247689505129755</v>
       </c>
       <c r="F1984" t="n">
         <v>0.03955320498606768</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042145</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.639985496319195</v>
+        <v>-4.768085445254146</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.019233463724059</v>
+        <v>0.967993484150079</v>
       </c>
       <c r="F1985" t="n">
         <v>0.03955320498606768</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078285</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.600054823141305</v>
+        <v>-4.728154772076255</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.033646437589469</v>
+        <v>0.9824064580154883</v>
       </c>
       <c r="F1986" t="n">
         <v>0.07948387816395802</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232398</v>
+        <v>3.864518876232402</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.5595844755786</v>
+        <v>-4.68768442451355</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.04478280485282</v>
+        <v>0.9935428252788401</v>
       </c>
       <c r="F1987" t="n">
         <v>0.119954225726663</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.494360294451394</v>
+        <v>-4.622460243386345</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.088059881396408</v>
+        <v>1.036819901822427</v>
       </c>
       <c r="F1988" t="n">
         <v>0.1851784068538686</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639822</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.544854584808451</v>
+        <v>-4.672954533743401</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.063823137552866</v>
+        <v>1.012583157978885</v>
       </c>
       <c r="F1989" t="n">
         <v>0.1401576697277944</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749925</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.564966240843159</v>
+        <v>-4.69306618977811</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.057035267470222</v>
+        <v>1.005795287896242</v>
       </c>
       <c r="F1990" t="n">
         <v>0.1511850147252136</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.662646820115805</v>
+        <v>-4.790746769050756</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.178520806782375</v>
+        <v>1.127280827208394</v>
       </c>
       <c r="F1991" t="n">
         <v>0.04048181938502476</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714888</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.638855251509662</v>
+        <v>-4.766955200444613</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.308150343442649</v>
+        <v>1.256910363868669</v>
       </c>
       <c r="F1992" t="n">
         <v>0.06427338799116705</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756014</v>
+        <v>3.814259761756017</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.675609670071385</v>
+        <v>-4.803709619006336</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.285156552031819</v>
+        <v>1.233916572457839</v>
       </c>
       <c r="F1993" t="n">
         <v>0.06427338799116705</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654188</v>
+        <v>3.803426852654192</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.671275367014337</v>
+        <v>-4.799375315949288</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.285083468838418</v>
+        <v>1.233843489264437</v>
       </c>
       <c r="F1994" t="n">
         <v>0.215923491310371</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717113</v>
+        <v>3.796293177717117</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.662382905621054</v>
+        <v>-4.790482854556005</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.306194859122522</v>
+        <v>1.254954879548542</v>
       </c>
       <c r="F1995" t="n">
         <v>0.215923491310371</v>
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.844614030643275</v>
+        <v>3.576895451488705</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.26755252407765</v>
+        <v>3.188438404334314</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.662382905621054</v>
+        <v>-4.790482854556005</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.306194859122522</v>
+        <v>1.254954879548542</v>
       </c>
       <c r="F1996" t="n">
         <v>0.215923491310371</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.260616321064017</v>
+        <v>3.181502201320682</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240615.xlsx
+++ b/tame_output/ON/bt/strategyON_20240615.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>-2.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-705.4%</t>
+          <t>-703.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-640.6%</t>
+          <t>-654.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-282.5%</t>
+          <t>-281.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-651.9%</t>
+          <t>873.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-250.7%</t>
+          <t>-256.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>305.1%</t>
+          <t>-147.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-202.4%</t>
+          <t>-215.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-127.9%</t>
+          <t>-137.3%</t>
         </is>
       </c>
     </row>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8678834074299461</v>
+        <v>-0.8472142432027547</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.773818975041</v>
+        <v>2.782086640731877</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.075449191821558</v>
+        <v>-1.054780027594367</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.688617457403596</v>
+        <v>2.696885123094472</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.493203215368395</v>
+        <v>-1.472534051141204</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.519442739489924</v>
+        <v>2.527710405180801</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.783334881973826</v>
+        <v>-1.762665717746635</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.403256289446674</v>
+        <v>2.41152395513755</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8814109797567796</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.991338940326904</v>
+        <v>-1.970669776099712</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.324946810659368</v>
+        <v>2.333214476350244</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8814109797567796</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.202751361214879</v>
+        <v>-2.182082196987688</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.235463298642166</v>
+        <v>2.243730964333042</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6699985588688046</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.568820088359531</v>
+        <v>-2.548150924132341</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.082120107090754</v>
+        <v>2.09038777278163</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3039298317241519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.777310869811216</v>
+        <v>-2.756641705584025</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.019062084248848</v>
+        <v>2.027329749939724</v>
       </c>
       <c r="F1852" t="n">
         <v>0.09543905027246746</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.024512054576437</v>
+        <v>-3.003842890349246</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.928280360751328</v>
+        <v>1.936548026442205</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1155924037712799</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.516897082600534</v>
+        <v>-3.496227918373343</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.732432741585422</v>
+        <v>1.740700407276298</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3767926242528168</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.902077473530607</v>
+        <v>-3.881408309303416</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.576903124026256</v>
+        <v>1.585170789717132</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.245760246757269</v>
+        <v>-4.225091082530079</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.441199138190207</v>
+        <v>1.449466803881083</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.452272023644291</v>
+        <v>-4.4316028594171</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.354700486091656</v>
+        <v>1.362968151782533</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.771616098724793</v>
+        <v>-4.750946934497602</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.228735782759715</v>
+        <v>1.237003448450591</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.20342189187458</v>
+        <v>-5.182752727647389</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.042346352967205</v>
+        <v>1.050614018658081</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.438115886007132</v>
+        <v>-5.417446721779942</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9367535303162744</v>
+        <v>0.9450211960071506</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.773778533237585</v>
+        <v>-5.753109369010394</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8010690630800585</v>
+        <v>0.8093367287709348</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.137404778137898</v>
+        <v>-6.116735613910707</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6621061253541747</v>
+        <v>0.6703737910450509</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.502532160776645</v>
+        <v>-6.481862996549454</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5153096873045073</v>
+        <v>0.5235773529953835</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.911120937957323</v>
+        <v>-6.890451773730133</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.350635720446995</v>
+        <v>0.3589033861378712</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.187697038273155</v>
+        <v>-7.167027874045965</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2351907127921229</v>
+        <v>0.2434583784829987</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.604088912560153</v>
+        <v>-7.583419748332963</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.06662801368620119</v>
+        <v>0.07489567937707697</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.874855001652798</v>
+        <v>-7.854185837425608</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.03141973128217801</v>
+        <v>-0.02315206559130178</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.220729823637607</v>
+        <v>-8.200060659410417</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1736700949304062</v>
+        <v>-0.16540242923953</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.384309701821991</v>
+        <v>-8.363640537594801</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2406971261491591</v>
+        <v>-0.2324294604582828</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.680971043632189</v>
+        <v>-8.660301879404999</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3555826869440302</v>
+        <v>-0.3473150212531539</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.867690751941492</v>
+        <v>-8.847021587714302</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4342968748021541</v>
+        <v>-0.4260292091112783</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.250692140684123</v>
+        <v>-9.230022976456933</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5875995316207909</v>
+        <v>-0.5793318659299147</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.432561931669158</v>
+        <v>-9.411892767441968</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6577759320433745</v>
+        <v>-0.6495082663524987</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.792092254173159</v>
+        <v>-9.771423089945969</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7962377577469248</v>
+        <v>-0.7879700920560491</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.842441317627381</v>
+        <v>-9.821772153400191</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8084613631714364</v>
+        <v>-0.8001936974805601</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.940060595048777</v>
+        <v>-9.919391430821587</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8444673235182258</v>
+        <v>-0.8361996578273501</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.08758668305442</v>
+        <v>-10.06691751882723</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9005842023989108</v>
+        <v>-0.892316536708035</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.29184485838428</v>
+        <v>-10.27117569415709</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9767742754122137</v>
+        <v>-0.968506609721338</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.36617783464445</v>
+        <v>-10.34550867041726</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.002024911431844</v>
+        <v>-0.993757245740968</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.442858704874723</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.292708002977</v>
+        <v>-10.27203883874981</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9572652772714427</v>
+        <v>-0.9489976115805669</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.369388873207274</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.46783242036354</v>
+        <v>-10.44716325613635</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.012759823478543</v>
+        <v>-1.004492157787667</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.544513290593818</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.70228451437803</v>
+        <v>-10.68161535015084</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.113759825985935</v>
+        <v>-1.105492160295059</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.544513290593818</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.80665924540448</v>
+        <v>-10.78599008117729</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.16218190917049</v>
+        <v>-1.153914243479614</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.648888021620264</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.85944540100481</v>
+        <v>-10.83877623677762</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.182180581572064</v>
+        <v>-1.173912915881188</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.744563508202661</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.98548219437309</v>
+        <v>-10.9648130301459</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.229901570290265</v>
+        <v>-1.221633904599389</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.719311885392918</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.93346668040428</v>
+        <v>-10.91279751617709</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.205105029016339</v>
+        <v>-1.196837363325463</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.719311885392918</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.0751385221284</v>
+        <v>-11.05446935790121</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.263248992604729</v>
+        <v>-1.254981326913853</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.719311885392918</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.02554767770357</v>
+        <v>-11.00487851347638</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.228359244669923</v>
+        <v>-1.220091578979047</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.669721040968084</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.01274028469879</v>
+        <v>-10.9920711204716</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.236287421114696</v>
+        <v>-1.228019755423821</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.718576815976986</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.78689513197938</v>
+        <v>-10.76622596775219</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.136370286990724</v>
+        <v>-1.128102621299847</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.676650140389822</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.66231647564179</v>
+        <v>-10.6416473114146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.085399679899627</v>
+        <v>-1.077132014208752</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.676650140389822</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.71521176368608</v>
+        <v>-10.69454259945889</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.103924020955234</v>
+        <v>-1.095656355264358</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.671694794301376</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.6430785883982</v>
+        <v>-10.62240942417101</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.069337046601445</v>
+        <v>-1.06106938091057</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.671694794301376</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.57171219578855</v>
+        <v>-10.55104303156136</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.050527751951452</v>
+        <v>-1.042260086260576</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.600328401691728</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.30787532858448</v>
+        <v>-10.28720616435729</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9548764863827315</v>
+        <v>-0.9466088206918557</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.600328401691728</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.04063352771608</v>
+        <v>-10.01996436348889</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8498143265347458</v>
+        <v>-0.84154666084387</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.600328401691728</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.94272648903959</v>
+        <v>-9.9220573248124</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8109518260376105</v>
+        <v>-0.8026841603467347</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.532342651831171</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.918772948063632</v>
+        <v>-9.898103783836442</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.800701903501734</v>
+        <v>-0.7924342378108578</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.508389110855214</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.654713009740835</v>
+        <v>-9.634043845513645</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7083382443343673</v>
+        <v>-0.7000705786434915</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.244329172532418</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.947633386235998</v>
+        <v>-8.926964222008808</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4282934285927333</v>
+        <v>-0.4200257629018571</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.244329172532418</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.907449087869807</v>
+        <v>-8.886779923642617</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4118760853584158</v>
+        <v>-0.4036084196675396</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.204144874166227</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.744049216930446</v>
+        <v>-8.723380052703256</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3471493157619143</v>
+        <v>-0.3388816500710381</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.040745003226864</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.510567994700846</v>
+        <v>-8.489898830473656</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2458323980322219</v>
+        <v>-0.2375647323413461</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.807263780997266</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.360901603693332</v>
+        <v>-8.340232439466142</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1888580519421756</v>
+        <v>-0.1805903862512994</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.71436028975473</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.228626130062445</v>
+        <v>-8.207956965835255</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1405803757427937</v>
+        <v>-0.1323127100519175</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.582084816123843</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.038026455389291</v>
+        <v>-8.017357291162101</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.06152544518589531</v>
+        <v>-0.05325777949501953</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.39148514145069</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.78902665670571</v>
+        <v>-7.76835749247852</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.05098081551119593</v>
+        <v>0.05924848120207171</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.39148514145069</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.894616646478815</v>
+        <v>-7.873947482251625</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1192311099972647</v>
+        <v>-0.1109634443063889</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.497075131223795</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.913351548597412</v>
+        <v>-7.892682384370222</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07818072896761707</v>
+        <v>-0.06991306327674129</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.502671140883926</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.765411507189812</v>
+        <v>-7.744742342962622</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1388836350927449</v>
+        <v>-0.1306159694018691</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.482350224975368</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.712441984935824</v>
+        <v>-7.691772820708634</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1264098124446278</v>
+        <v>-0.118142146753752</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.429380702721379</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.668893578165133</v>
+        <v>-7.648224413937943</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1159510618314448</v>
+        <v>-0.107683396140569</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.429380702721379</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.426745184711275</v>
+        <v>-7.406076020484085</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.00462935006875842</v>
+        <v>0.003638315622117361</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.429380702721379</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722815</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.318486047588753</v>
+        <v>-7.297816883361564</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.03320642523944528</v>
+        <v>0.04147409093032106</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.429380702721379</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.195194912771623</v>
+        <v>-7.174525748544433</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.0800209731768744</v>
+        <v>0.08828863886775062</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.306089567904249</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.174045713868179</v>
+        <v>-7.153376549640989</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.09618163097557719</v>
+        <v>0.104449296666453</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.284940369000806</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.930280271884735</v>
+        <v>-6.909611107657545</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1894685161160052</v>
+        <v>0.1977361818068815</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.284940369000806</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.82851745160744</v>
+        <v>-6.80784828738025</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2322979581469395</v>
+        <v>0.2405656238378153</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.271721300608377</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.578667057658365</v>
+        <v>-6.557997893431176</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3249801907102712</v>
+        <v>0.3332478564011474</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.271721300608377</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.402774965190932</v>
+        <v>-6.382105800963743</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3989361512178933</v>
+        <v>0.4072038169087691</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.271721300608377</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.231328502168469</v>
+        <v>-6.210659337941279</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4808422424814323</v>
+        <v>0.4891099081723085</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.100274837585914</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.006295502499646</v>
+        <v>-5.985626338272456</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5698759199652588</v>
+        <v>0.5781435856561346</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8752418379170909</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.942659760265712</v>
+        <v>-5.921990596038522</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6000250179131497</v>
+        <v>0.6082926836040254</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8116060956831563</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.89889757895987</v>
+        <v>-5.87822841473268</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5987241492192821</v>
+        <v>0.6069918149101579</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8116060956831563</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.65846708215501</v>
+        <v>-5.63779791792782</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6966394245661034</v>
+        <v>0.7049070902569792</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5711755988782961</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.586224513983815</v>
+        <v>-5.565555349756625</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7294657656694015</v>
+        <v>0.7377334313602772</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5711755988782961</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.533226191702427</v>
+        <v>-5.512557027475237</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7513436784992966</v>
+        <v>0.7596113441901724</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5158393398763572</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.4244213062227</v>
+        <v>-5.40375214199551</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7918637039111811</v>
+        <v>0.8001313696020569</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5158393398763572</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.20440050818569</v>
+        <v>-5.1837313439585</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8814510601365995</v>
+        <v>0.8897187258274752</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.374619494808377</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.071532819122412</v>
+        <v>-5.050863654895222</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9504923185637337</v>
+        <v>0.9587599842546095</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.374619494808377</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.951359735757913</v>
+        <v>-4.930690571530723</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9997073963498351</v>
+        <v>1.007975062040711</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.254446411443878</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.806687590658176</v>
+        <v>-4.786018426430986</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.06766435695117</v>
+        <v>1.075932022642046</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.1097742663441406</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.866562418015868</v>
+        <v>-4.845893253788678</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.029751917409519</v>
+        <v>1.038019583100395</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1696490937018327</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.779762920236859</v>
+        <v>-4.759093756009669</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.086872209843688</v>
+        <v>1.095139875534564</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1696490937018327</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.782232626698665</v>
+        <v>-4.761563462471475</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.085956728632378</v>
+        <v>1.094224394323254</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1721188001636389</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.850602813022675</v>
+        <v>-4.829933648795485</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.069615576577476</v>
+        <v>1.077883242268352</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.162843101127424</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.959140993938809</v>
+        <v>-4.938471829711619</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.016637012842914</v>
+        <v>1.02490467853379</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.162843101127424</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.990134153267515</v>
+        <v>-4.969464989040325</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8289493141518185</v>
+        <v>0.8372169798426945</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.162843101127424</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.814659893475046</v>
+        <v>-4.793990729247856</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9037062500605939</v>
+        <v>0.9119739157514699</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.162843101127424</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.925596146116295</v>
+        <v>-4.904926981889105</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8350737777653015</v>
+        <v>0.8433414434561772</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.162843101127424</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.933878220261353</v>
+        <v>-4.913209056034163</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8348923333271836</v>
+        <v>0.8431599990180594</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1711251752724823</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.87402560105763</v>
+        <v>-4.85335643683044</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8690057674408052</v>
+        <v>0.8772734331316812</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1711251752724823</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.787782138031252</v>
+        <v>-4.767112973804062</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8984494232252165</v>
+        <v>0.9067170889160925</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1711251752724823</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.833088957430232</v>
+        <v>-4.812419793203042</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8721024709101501</v>
+        <v>0.8803701366010261</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2119353382817131</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.862122062132533</v>
+        <v>-4.841452897905343</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8610411020623312</v>
+        <v>0.8693087677532072</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2119353382817131</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.769311580681673</v>
+        <v>-4.748642416454484</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8274379865340409</v>
+        <v>0.8357056522249167</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1191248568308538</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.813701050011101</v>
+        <v>-4.793031885783911</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8115556747268706</v>
+        <v>0.8198233404177466</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1635143261602814</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.701029831774851</v>
+        <v>-4.680360667547661</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8516998705330936</v>
+        <v>0.8599675362239696</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.05084310792403124</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.588652830592178</v>
+        <v>-4.567983666364988</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.90214196683683</v>
+        <v>0.910409632527706</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.05084310792403124</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.786887399478909</v>
+        <v>-4.766218235251719</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8343453410506769</v>
+        <v>0.8426130067415527</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2490776768107618</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.869888680504188</v>
+        <v>-4.849219516276998</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6395005486412186</v>
+        <v>0.6477682143320944</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2676485613379356</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.978502758947519</v>
+        <v>-4.957833594720329</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7162045779830917</v>
+        <v>0.7244722436739677</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2676485613379356</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.065101341928622</v>
+        <v>-5.044432177701432</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6960781708929735</v>
+        <v>0.7043458365838493</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2676485613379356</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.026717679370471</v>
+        <v>-5.006048515143281</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7088510772586027</v>
+        <v>0.7171187429494785</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2292648987797844</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.849601349335305</v>
+        <v>-4.828932185108115</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.776426638117971</v>
+        <v>0.784694303808847</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2292648987797844</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.89469359416885</v>
+        <v>-4.87402442994166</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7590731319464659</v>
+        <v>0.7673407976373419</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2911609419491742</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.715318172930083</v>
+        <v>-4.694649008702893</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8246102757483873</v>
+        <v>0.8328779414392633</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1343841837784555</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982233</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.760332386450688</v>
+        <v>-4.739663222223498</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7874120456717346</v>
+        <v>0.7956797113626106</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1647330790930601</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.027336896723123</v>
+        <v>-5.006667732495933</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6863018039017064</v>
+        <v>0.6945694695925824</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3590961171360087</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.128534678160296</v>
+        <v>-5.107865513933106</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6450266132233389</v>
+        <v>0.6532942789142147</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4275049306813279</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.096059091989524</v>
+        <v>-5.075389927762334</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6556168092459642</v>
+        <v>0.6638844749368404</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4275049306813279</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.077020964282227</v>
+        <v>-5.056351800055037</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6597567795371284</v>
+        <v>0.6680244452280042</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4856885420125224</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.108147595432845</v>
+        <v>-5.087478431205655</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8248879960155615</v>
+        <v>0.8331556617064373</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4856885420125224</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.160467976033637</v>
+        <v>-5.139798811806447</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8047931727613782</v>
+        <v>0.8130608384522544</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4507416820036503</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.180725274562595</v>
+        <v>-5.160056110335405</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8026987837467212</v>
+        <v>0.810966449437597</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4507416820036503</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.032982304327592</v>
+        <v>-5.012313140100402</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9409486196327439</v>
+        <v>0.9492162853236201</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2829343247687671</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.134996986858813</v>
+        <v>-5.114327822631624</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9029363681517366</v>
+        <v>0.9112040338426124</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2829343247687671</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394733</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.128844280806029</v>
+        <v>-5.108175116578839</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9060597989645087</v>
+        <v>0.9143274646553845</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2767816187159828</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.145653578956531</v>
+        <v>-5.124984414729341</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8984165564444182</v>
+        <v>0.906684222135294</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2935909168664845</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.083355580180409</v>
+        <v>-5.062686415953219</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9896713097516878</v>
+        <v>0.9979389754425636</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2935909168664845</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992196</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.881565382515251</v>
+        <v>-4.860896218288061</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7789682612071491</v>
+        <v>0.7872359268980249</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.09557272469733008</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.821674700872657</v>
+        <v>-4.801005536645468</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8732147661863616</v>
+        <v>0.8814824318772376</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.0356820430547366</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319551</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.919415245497632</v>
+        <v>-4.898746081270442</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8487462844524154</v>
+        <v>0.8570139501432914</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.05157132118771679</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.095753005620561</v>
+        <v>-5.075083841393371</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7767471612279153</v>
+        <v>0.7850148269187915</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2279090813106462</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.024206682843684</v>
+        <v>-5.003537518616494</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8038573083785949</v>
+        <v>0.8121249740694707</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2279090813106462</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.979833551205116</v>
+        <v>-4.959164386977926</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8214694284694584</v>
+        <v>0.8297370941603344</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1835359496720776</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863229</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.971879580910343</v>
+        <v>-4.951210416683153</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8246510165873673</v>
+        <v>0.8329186822782433</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1835359496720776</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947588</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.924223850349287</v>
+        <v>-4.903554686122098</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8500950658395943</v>
+        <v>0.8583627315304703</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1358802191110219</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326881</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.796539540554991</v>
+        <v>-4.775870376327801</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9060611631320377</v>
+        <v>0.9143288288229137</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.00819590931672548</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314556</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.85720613095738</v>
+        <v>-4.83653696673019</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8685491994469543</v>
+        <v>0.8768168651378303</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.08989422603525915</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690032</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.812367729348981</v>
+        <v>-4.791698565121791</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8905822627009423</v>
+        <v>0.8988499283918183</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.08535079309038968</v>
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674316</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.755251175811763</v>
+        <v>-4.892457200878789</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9175898237469078</v>
+        <v>0.8627074137200972</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.0416235338911633</v>
+        <v>-0.1741763618173951</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.795072598050663</v>
+        <v>2.715540901294923</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163225</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.711048338725862</v>
+        <v>-4.848254363792889</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9411505611091051</v>
+        <v>0.8862681510822945</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.002579303194737148</v>
+        <v>-0.1299735247314946</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.82747390283004</v>
+        <v>2.747942206074301</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83822866302291</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.748027366389305</v>
+        <v>-4.885233391456332</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9247689505129755</v>
+        <v>0.8698865404861649</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.03955320498606768</v>
+        <v>-0.09299962294016412</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.848068244374086</v>
+        <v>2.768536547618347</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042145</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.768085445254146</v>
+        <v>-4.905291470321172</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.967993484150079</v>
+        <v>0.9131110741232682</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.03955320498606768</v>
+        <v>-0.09299962294016412</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.899316009557126</v>
+        <v>2.819784312801386</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078285</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.728154772076255</v>
+        <v>-4.865360797143282</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9824064580154883</v>
+        <v>0.9275240479886775</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.07948387816395802</v>
+        <v>-0.05306894976227378</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.921715118058113</v>
+        <v>2.842183421302374</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232402</v>
+        <v>3.864518876232398</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.68768442451355</v>
+        <v>-4.824890449580577</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9935428252788401</v>
+        <v>0.9386604152520295</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.119954225726663</v>
+        <v>-0.01259860219956882</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.940945554834006</v>
+        <v>2.861413858078266</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.622460243386345</v>
+        <v>-4.759666268453372</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.036819901822427</v>
+        <v>0.9819374917956165</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1851784068538686</v>
+        <v>0.05262557892763681</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.997267467603034</v>
+        <v>2.917735770847295</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639822</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.672954533743401</v>
+        <v>-4.810160558810428</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.012583157978885</v>
+        <v>0.9577007479520745</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1401576697277944</v>
+        <v>0.007604841801562567</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.96621599762667</v>
+        <v>2.886684300870931</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749925</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.69306618977811</v>
+        <v>-4.830272214845136</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.005795287896242</v>
+        <v>0.9509128778694316</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1511850147252136</v>
+        <v>0.01863218679898176</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.974089196956362</v>
+        <v>2.894557500200623</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393551</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.790746769050756</v>
+        <v>-4.927952794117783</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.127280827208394</v>
+        <v>1.072398417181584</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.04048181938502476</v>
+        <v>-0.09207100854120703</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.068225050773459</v>
+        <v>2.98869335401772</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714888</v>
+        <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.766955200444613</v>
+        <v>-4.90416122551164</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.256910363868669</v>
+        <v>1.202027953841858</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.06427338799116705</v>
+        <v>-0.06827943993506475</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.202612901154962</v>
+        <v>3.123081204399222</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756017</v>
+        <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.803709619006336</v>
+        <v>-4.940915644073362</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.233916572457839</v>
+        <v>1.179034162431028</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.06427338799116705</v>
+        <v>-0.06827943993506475</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.194320877168821</v>
+        <v>3.114789180413081</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654192</v>
+        <v>3.803426852654188</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.799375315949288</v>
+        <v>-4.936581341016314</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.233843489264437</v>
+        <v>1.178961079237627</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.215923491310371</v>
+        <v>0.08337066338413918</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.283504134744123</v>
+        <v>3.203972437988384</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717117</v>
+        <v>3.796293177717114</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.790482854556005</v>
+        <v>-4.927688879623031</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.254954879548542</v>
+        <v>1.200072469521731</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.215923491310371</v>
+        <v>0.08337066338413918</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.301058540470914</v>
+        <v>3.221526843715175</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.576895451488705</v>
+        <v>3.576895451488702</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.188438404334314</v>
+        <v>3.094294814507915</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.790482854556005</v>
+        <v>-4.927688879623031</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.254954879548542</v>
+        <v>1.200072469521731</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.215923491310371</v>
+        <v>0.08337066338413918</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.181502201320682</v>
+        <v>3.087358611494282</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240615.xlsx
+++ b/tame_output/ON/bt/strategyON_20240615.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-703.3%</t>
+          <t>-692.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.5%</t>
+          <t>449.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-654.3%</t>
+          <t>-644.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.7%</t>
+          <t>-277.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>873.2%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-256.2%</t>
+          <t>-247.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-100.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-215.7%</t>
+          <t>-198.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-137.3%</t>
+          <t>-108.4%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8472142432027547</v>
+        <v>-0.7397834584949903</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.782086640731877</v>
+        <v>2.825058954614982</v>
       </c>
       <c r="F1845" t="n">
         <v>1.482648992955049</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.054780027594367</v>
+        <v>-0.9473492428866022</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.696885123094472</v>
+        <v>2.739857436977578</v>
       </c>
       <c r="F1846" t="n">
         <v>1.275083208563437</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.472534051141204</v>
+        <v>-1.365103266433439</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.527710405180801</v>
+        <v>2.570682719063906</v>
       </c>
       <c r="F1847" t="n">
         <v>0.8573291850165997</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.762665717746635</v>
+        <v>-1.65523493303887</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.41152395513755</v>
+        <v>2.454496269020656</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8814109797567796</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.970669776099712</v>
+        <v>-1.863238991391948</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.333214476350244</v>
+        <v>2.37618679023335</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8814109797567796</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.182082196987688</v>
+        <v>-2.074651412279923</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.243730964333042</v>
+        <v>2.286703278216148</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6699985588688046</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.548150924132341</v>
+        <v>-2.440720139424576</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.09038777278163</v>
+        <v>2.133360086664736</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3039298317241519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.756641705584025</v>
+        <v>-2.649210920876261</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.027329749939724</v>
+        <v>2.07030206382283</v>
       </c>
       <c r="F1852" t="n">
         <v>0.09543905027246746</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.003842890349246</v>
+        <v>-2.896412105641482</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.936548026442205</v>
+        <v>1.97952034032531</v>
       </c>
       <c r="F1853" t="n">
         <v>0.1155924037712799</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.496227918373343</v>
+        <v>-3.388797133665579</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.740700407276298</v>
+        <v>1.783672721159404</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.3767926242528168</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.881408309303416</v>
+        <v>-3.773977524595651</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.585170789717132</v>
+        <v>1.628143103600238</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.225091082530079</v>
+        <v>-4.117660297822314</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.449466803881083</v>
+        <v>1.492439117764189</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.4316028594171</v>
+        <v>-4.324172074709336</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.362968151782533</v>
+        <v>1.405940465665638</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.750946934497602</v>
+        <v>-4.643516149789837</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.237003448450591</v>
+        <v>1.279975762333697</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.182752727647389</v>
+        <v>-5.075321942939625</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.050614018658081</v>
+        <v>1.093586332541187</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.417446721779942</v>
+        <v>-5.310015937072177</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9450211960071506</v>
+        <v>0.9879935098902566</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.753109369010394</v>
+        <v>-5.64567858430263</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8093367287709348</v>
+        <v>0.8523090426540407</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.116735613910707</v>
+        <v>-6.009304829202943</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6703737910450509</v>
+        <v>0.7133461049281569</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.481862996549454</v>
+        <v>-6.37443221184169</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5235773529953835</v>
+        <v>0.5665496668784895</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.890451773730133</v>
+        <v>-6.783020989022368</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3589033861378712</v>
+        <v>0.4018757000209767</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.167027874045965</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2434583784829987</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.583419748332963</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.07489567937707697</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.854185837425608</v>
+        <v>-7.746755052717844</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.02315206559130178</v>
+        <v>0.01982024829180373</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.200060659410417</v>
+        <v>-8.092629874702652</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.16540242923953</v>
+        <v>-0.1224301153564245</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.363640537594801</v>
+        <v>-8.256209752887036</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2324294604582828</v>
+        <v>-0.1894571465751773</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.660301879404999</v>
+        <v>-8.552871094697235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3473150212531539</v>
+        <v>-0.3043427073700484</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.847021587714302</v>
+        <v>-8.739590803006537</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4260292091112783</v>
+        <v>-0.3830568952281723</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.230022976456933</v>
+        <v>-9.122592191749169</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5793318659299147</v>
+        <v>-0.5363595520468092</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.411892767441968</v>
+        <v>-9.304461982734203</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6495082663524987</v>
+        <v>-0.6065359524693927</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.771423089945969</v>
+        <v>-9.663992305238205</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7879700920560491</v>
+        <v>-0.7449977781729431</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.821772153400191</v>
+        <v>-9.714341368692427</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8001936974805601</v>
+        <v>-0.7572213835974546</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.919391430821587</v>
+        <v>-9.811960646113823</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8361996578273501</v>
+        <v>-0.7932273439442441</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.06691751882723</v>
+        <v>-9.959486734119466</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.892316536708035</v>
+        <v>-0.8493442228249291</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.27117569415709</v>
+        <v>-10.16374490944933</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.968506609721338</v>
+        <v>-0.925534295838232</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.34550867041726</v>
+        <v>-10.23807788570949</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.993757245740968</v>
+        <v>-0.9507849318578621</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.442858704874723</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.27203883874981</v>
+        <v>-10.16460805404204</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9489976115805669</v>
+        <v>-0.906025297697461</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.369388873207274</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.44716325613635</v>
+        <v>-10.33973247142859</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.004492157787667</v>
+        <v>-0.9615198439045614</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.544513290593818</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.68161535015084</v>
+        <v>-10.57418456544308</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.105492160295059</v>
+        <v>-1.062519846411953</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.544513290593818</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.78599008117729</v>
+        <v>-10.67855929646952</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.153914243479614</v>
+        <v>-1.110941929596508</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.648888021620264</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.83877623677762</v>
+        <v>-10.73134545206985</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.173912915881188</v>
+        <v>-1.130940601998082</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.744563508202661</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.9648130301459</v>
+        <v>-10.85738224543814</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.221633904599389</v>
+        <v>-1.178661590716283</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.719311885392918</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.91279751617709</v>
+        <v>-10.80536673146933</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.196837363325463</v>
+        <v>-1.153865049442357</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.719311885392918</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.05446935790121</v>
+        <v>-10.94703857319345</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.254981326913853</v>
+        <v>-1.212009013030747</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.719311885392918</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.00487851347638</v>
+        <v>-10.89744772876861</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.220091578979047</v>
+        <v>-1.177119265095941</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.669721040968084</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.9920711204716</v>
+        <v>-10.88464033576384</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.228019755423821</v>
+        <v>-1.185047441540715</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.718576815976986</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.76622596775219</v>
+        <v>-10.65879518304443</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.128102621299847</v>
+        <v>-1.085130307416742</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.676650140389822</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.6416473114146</v>
+        <v>-10.53421652670684</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.077132014208752</v>
+        <v>-1.034159700325647</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.676650140389822</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.69454259945889</v>
+        <v>-10.58711181475112</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.095656355264358</v>
+        <v>-1.052684041381253</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.671694794301376</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.62240942417101</v>
+        <v>-10.51497863946324</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.06106938091057</v>
+        <v>-1.018097067027464</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.671694794301376</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.55104303156136</v>
+        <v>-10.4436122468536</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.042260086260576</v>
+        <v>-0.9992877723774711</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.600328401691728</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.28720616435729</v>
+        <v>-10.17977537964953</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9466088206918557</v>
+        <v>-0.9036365068087506</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.600328401691728</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.01996436348889</v>
+        <v>-9.912533578781128</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.84154666084387</v>
+        <v>-0.7985743469607649</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.600328401691728</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.9220573248124</v>
+        <v>-9.814626540104637</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8026841603467347</v>
+        <v>-0.7597118464636297</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.532342651831171</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.898103783836442</v>
+        <v>-9.790672999128679</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7924342378108578</v>
+        <v>-0.7494619239277527</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.508389110855214</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.634043845513645</v>
+        <v>-9.526613060805882</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7000705786434915</v>
+        <v>-0.6570982647603865</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.244329172532418</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.926964222008808</v>
+        <v>-8.819533437301045</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4200257629018571</v>
+        <v>-0.377053449018752</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.244329172532418</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.886779923642617</v>
+        <v>-8.779349138934855</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4036084196675396</v>
+        <v>-0.3606361057844345</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.204144874166227</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.723380052703256</v>
+        <v>-8.615949267995493</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3388816500710381</v>
+        <v>-0.295909336187933</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.040745003226864</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.489898830473656</v>
+        <v>-8.382468045765894</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2375647323413461</v>
+        <v>-0.194592418458241</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.807263780997266</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.340232439466142</v>
+        <v>-8.232801654758379</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1805903862512994</v>
+        <v>-0.1376180723681943</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.71436028975473</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.207956965835255</v>
+        <v>-8.100526181127492</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1323127100519175</v>
+        <v>-0.0893403961688124</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.582084816123843</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.017357291162101</v>
+        <v>-7.909926506454339</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.05325777949501953</v>
+        <v>-0.0102854656119149</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.39148514145069</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.76835749247852</v>
+        <v>-7.660926707770758</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.05924848120207171</v>
+        <v>0.1022207950851763</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.39148514145069</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.873947482251625</v>
+        <v>-7.766516697543863</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1109634443063889</v>
+        <v>-0.06799113042328386</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.497075131223795</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.892682384370222</v>
+        <v>-7.78525159966246</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.06991306327674129</v>
+        <v>-0.02694074939363666</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.502671140883926</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.744742342962622</v>
+        <v>-7.637311558254861</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1306159694018691</v>
+        <v>-0.08764365551876452</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.482350224975368</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.691772820708634</v>
+        <v>-7.584342036000872</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.118142146753752</v>
+        <v>-0.07516983287064694</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.429380702721379</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.648224413937943</v>
+        <v>-7.540793629230182</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.107683396140569</v>
+        <v>-0.06471108225746391</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.429380702721379</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.406076020484085</v>
+        <v>-7.298645235776323</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.003638315622117361</v>
+        <v>0.04661062950522243</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.429380702721379</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.297816883361564</v>
+        <v>-7.190386098653802</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.04147409093032106</v>
+        <v>0.08444640481342613</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.429380702721379</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.174525748544433</v>
+        <v>-7.067094963836671</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.08828863886775062</v>
+        <v>0.1312609527508553</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.306089567904249</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.153376549640989</v>
+        <v>-7.045945764933228</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.104449296666453</v>
+        <v>0.1474216105495576</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.284940369000806</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.909611107657545</v>
+        <v>-6.802180322949783</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1977361818068815</v>
+        <v>0.2407084956899861</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.284940369000806</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.80784828738025</v>
+        <v>-6.700417502672488</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2405656238378153</v>
+        <v>0.28353793772092</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.271721300608377</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279181</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.557997893431176</v>
+        <v>-6.450567108723414</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3332478564011474</v>
+        <v>0.376220170284252</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.271721300608377</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.382105800963743</v>
+        <v>-6.274675016255982</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4072038169087691</v>
+        <v>0.4501761307918737</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.271721300608377</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.210659337941279</v>
+        <v>-6.103228553233518</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4891099081723085</v>
+        <v>0.5320822220554127</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.100274837585914</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.985626338272456</v>
+        <v>-5.878195553564695</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5781435856561346</v>
+        <v>0.6211158995392387</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8752418379170909</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.921990596038522</v>
+        <v>-5.814559811330761</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6082926836040254</v>
+        <v>0.6512649974871301</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8116060956831563</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.87822841473268</v>
+        <v>-5.770797630024919</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6069918149101579</v>
+        <v>0.649964128793262</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8116060956831563</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.63779791792782</v>
+        <v>-5.530367133220059</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7049070902569792</v>
+        <v>0.7478794041400838</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5711755988782961</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.565555349756625</v>
+        <v>-5.458124565048864</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7377334313602772</v>
+        <v>0.7807057452433819</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5711755988782961</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.512557027475237</v>
+        <v>-5.405126242767476</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7596113441901724</v>
+        <v>0.802583658073277</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5158393398763572</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.40375214199551</v>
+        <v>-5.296321357287749</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8001313696020569</v>
+        <v>0.8431036834851611</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5158393398763572</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.1837313439585</v>
+        <v>-5.076300559250739</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8897187258274752</v>
+        <v>0.9326910397105794</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.374619494808377</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.050863654895222</v>
+        <v>-4.943432870187461</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9587599842546095</v>
+        <v>1.001732298137714</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.374619494808377</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.930690571530723</v>
+        <v>-4.823259786822963</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.007975062040711</v>
+        <v>1.050947375923815</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.254446411443878</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.786018426430986</v>
+        <v>-4.678587641723225</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.075932022642046</v>
+        <v>1.11890433652515</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.1097742663441406</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.845893253788678</v>
+        <v>-4.738462469080917</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.038019583100395</v>
+        <v>1.080991896983499</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1696490937018327</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.759093756009669</v>
+        <v>-4.651662971301908</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.095139875534564</v>
+        <v>1.138112189417669</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1696490937018327</v>
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.045936603717144</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.761563462471475</v>
+        <v>-4.654132677763714</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.094224394323254</v>
+        <v>1.183927108297911</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1721188001636389</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.895934923527408</v>
+        <v>2.942665323618961</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.056943526191847</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.829933648795485</v>
+        <v>-4.722502864087724</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.077883242268352</v>
+        <v>1.16758595624301</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.162843101127424</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.91250726542384</v>
+        <v>2.959237665515392</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.047380234823738</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.938471829711619</v>
+        <v>-4.831041045003858</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.02490467853379</v>
+        <v>1.114607392508447</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.162843101127424</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.902943974055731</v>
+        <v>2.949674374147284</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.872089799864125</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.969464989040325</v>
+        <v>-4.862034204332564</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8372169798426945</v>
+        <v>0.9269196938173518</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.162843101127424</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.727653539096118</v>
+        <v>2.774383939187671</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.876657031855912</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.793990729247856</v>
+        <v>-4.686559944540095</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9119739157514699</v>
+        <v>1.001676629726127</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.162843101127424</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.732220771087905</v>
+        <v>2.778951171179458</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.852399060617119</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.904926981889105</v>
+        <v>-4.797496197181344</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8433414434561772</v>
+        <v>0.9330441574308346</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.162843101127424</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.707962799849112</v>
+        <v>2.754693199940665</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.77321029711129</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.855530445837025</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.913209056034163</v>
+        <v>-4.805778271326402</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8431599990180594</v>
+        <v>0.9328627129927167</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1711251752724823</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.706124940581983</v>
+        <v>2.752855340673536</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264159</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.865702832269157</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.85335643683044</v>
+        <v>-4.745925652122679</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8772734331316812</v>
+        <v>0.9669761471063385</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1711251752724823</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.716297327014115</v>
+        <v>2.763027727105668</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742295</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.860649102843018</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.767112973804062</v>
+        <v>-4.659682189096301</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9067170889160925</v>
+        <v>0.9964198028907498</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1711251752724823</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.711243597587976</v>
+        <v>2.757973997679529</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.852424878287543</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.812419793203042</v>
+        <v>-4.704989008495281</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8803701366010261</v>
+        <v>0.9700728505756835</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2119353382817131</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.678533275226963</v>
+        <v>2.725263675318516</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.852976751320645</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.841452897905343</v>
+        <v>-4.734022113197582</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8693087677532072</v>
+        <v>0.9590114817278645</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2119353382817131</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.679085148260064</v>
+        <v>2.725815548351617</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.78224944321201</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.748642416454484</v>
+        <v>-4.641211631746723</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8357056522249167</v>
+        <v>0.925408366199574</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1191248568308538</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.664044129021946</v>
+        <v>2.710774529113499</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.784122919136611</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.793031885783911</v>
+        <v>-4.68560110107615</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8198233404177466</v>
+        <v>0.909526054392404</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1635143261602814</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.63928392334889</v>
+        <v>2.686014323440443</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.779198627648334</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.680360667547661</v>
+        <v>-4.5729298828399</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8599675362239696</v>
+        <v>0.9496702501986269</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.05084310792403124</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.701962362802363</v>
+        <v>2.748692762893916</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.784689923479001</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.567983666364988</v>
+        <v>-4.564109821203878</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.910409632527706</v>
+        <v>0.9586895706837029</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.05084310792403124</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.70745365863303</v>
+        <v>2.754184058724583</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.796187125247541</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.766218235251719</v>
+        <v>-4.762344390090609</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8426130067415527</v>
+        <v>0.8908929448975496</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2490776768107618</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.600010119069531</v>
+        <v>2.646740519161084</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705321</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.634542845248194</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.849219516276998</v>
+        <v>-4.845345671115888</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6477682143320944</v>
+        <v>0.6960481524880913</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2676485613379356</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.42722330835388</v>
+        <v>2.473953708445433</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.754692505967399</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.957833594720329</v>
+        <v>-4.953959749559219</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7244722436739677</v>
+        <v>0.7727521818299645</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2676485613379356</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.547372969073086</v>
+        <v>2.594103369164638</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.769205532069722</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.044432177701432</v>
+        <v>-5.040558332540322</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7043458365838493</v>
+        <v>0.7526257747398462</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2676485613379356</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.561885995175408</v>
+        <v>2.608616395266961</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.74117406991342</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.766624973412091</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.006048515143281</v>
+        <v>-5.002174669982171</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7171187429494785</v>
+        <v>0.7653986811054754</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2292648987797844</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.582335634052668</v>
+        <v>2.629066034144221</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.763354002257393</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.828932185108115</v>
+        <v>-4.825058339947005</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.784694303808847</v>
+        <v>0.8329742419648438</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2292648987797844</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.57906466289797</v>
+        <v>2.625795062989523</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793897</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.764037394019306</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.87402442994166</v>
+        <v>-4.870150584780551</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7673407976373419</v>
+        <v>0.8156207357933385</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2911609419491742</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.542610428758249</v>
+        <v>2.589340828849802</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.757824369325721</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.694649008702893</v>
+        <v>-4.690775163541783</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8328779414392633</v>
+        <v>0.8811578795952599</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1343841837784555</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.630463458967094</v>
+        <v>2.677193859058647</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.73863182465731</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.739663222223498</v>
+        <v>-4.735789377062389</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7956797113626106</v>
+        <v>0.8439596495186075</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1647330790930601</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.593061577109922</v>
+        <v>2.639791977201475</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.744323386996256</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.006667732495933</v>
+        <v>-5.002793887334824</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6945694695925824</v>
+        <v>0.7428494077485792</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3590961171360087</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.482135316623098</v>
+        <v>2.528865716714651</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.743527308892757</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.107865513933106</v>
+        <v>-5.103991668771997</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6532942789142147</v>
+        <v>0.7015742170702115</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4275049306813279</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.440293950392408</v>
+        <v>2.487024350483961</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.741127270447074</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.075389927762334</v>
+        <v>-5.071516082601224</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6638844749368404</v>
+        <v>0.7121644130928373</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4275049306813279</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.437893911946725</v>
+        <v>2.484624312038278</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.737651989655319</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.056351800055037</v>
+        <v>-5.052477954893927</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6680244452280042</v>
+        <v>0.716304383384001</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4856885420125224</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.399508464356253</v>
+        <v>2.446238864447806</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.915233858594</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.087478431205655</v>
+        <v>-5.083604586044546</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8331556617064373</v>
+        <v>0.8814355998624341</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4856885420125224</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.577090333294934</v>
+        <v>2.623820733386486</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.916067187580133</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.139798811806447</v>
+        <v>-5.135924966645337</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8130608384522544</v>
+        <v>0.8613407766082508</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4507416820036503</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.598891778286391</v>
+        <v>2.645622178377943</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.922075717977059</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.160056110335405</v>
+        <v>-5.156182265174295</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.810966449437597</v>
+        <v>0.8592463875935938</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4507416820036503</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.604900308683316</v>
+        <v>2.651630708774869</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.001228365769081</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.012313140100402</v>
+        <v>-5.008439294939293</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9492162853236201</v>
+        <v>0.9974962234796168</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2829343247687671</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.784737370816268</v>
+        <v>2.831467770907821</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.004021987300562</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.114327822631624</v>
+        <v>-5.110453977470514</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9112040338426124</v>
+        <v>0.9594839719986092</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2829343247687671</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.787530992347749</v>
+        <v>2.834261392439302</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.00468433569222</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.108175116578839</v>
+        <v>-5.10430127141773</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9143274646553845</v>
+        <v>0.9626074028113814</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2767816187159828</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.791884964371078</v>
+        <v>2.838615364462631</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.003764812432331</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.124984414729341</v>
+        <v>-5.121110569568232</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.906684222135294</v>
+        <v>0.9549641602912908</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2935909168664845</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.780879862220887</v>
+        <v>2.82761026231244</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.070100366229152</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.062686415953219</v>
+        <v>-5.058812570792109</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9979389754425636</v>
+        <v>1.04621891359856</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2935909168664845</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.847215416017708</v>
+        <v>2.893945816109261</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.77868123861855</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.860896218288061</v>
+        <v>-4.857022373126951</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7872359268980249</v>
+        <v>0.8355158650540218</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.09557272469733008</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.674607203708599</v>
+        <v>2.721337603800152</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.848971470940725</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.801005536645468</v>
+        <v>-4.797131691484358</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8814824318772376</v>
+        <v>0.9297623700332343</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.0356820430547366</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.78083184501633</v>
+        <v>2.827562245107883</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.863599207056768</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.898746081270442</v>
+        <v>-4.894872236109332</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8570139501432914</v>
+        <v>0.9052938882992883</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.05157132118771679</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.785926014252586</v>
+        <v>2.832656414344139</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.86213518788144</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.075083841393371</v>
+        <v>-5.071209996232262</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7850148269187915</v>
+        <v>0.8332947650747879</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2279090813106462</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.6786593390035</v>
+        <v>2.725389739095053</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.860626805921369</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.003537518616494</v>
+        <v>-4.999663673455385</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8121249740694707</v>
+        <v>0.8604049122254676</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2279090813106462</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.677150957043428</v>
+        <v>2.723881357134981</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.860489673356805</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.959164386977926</v>
+        <v>-4.955290541816816</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8297370941603344</v>
+        <v>0.8780170323163312</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1835359496720776</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.703637703462006</v>
+        <v>2.750368103553559</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.860489673356805</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.951210416683153</v>
+        <v>-4.947336571522044</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8329186822782433</v>
+        <v>0.8811986204342399</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1835359496720776</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.703637703462006</v>
+        <v>2.750368103553559</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.866871430384609</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.903554686122098</v>
+        <v>-4.899680840960988</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8583627315304703</v>
+        <v>0.9066426696864669</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1358802191110219</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.738612898826444</v>
+        <v>2.785343298917997</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.871763803759334</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.775870376327801</v>
+        <v>-4.771996531166692</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9143288288229137</v>
+        <v>0.9626087669789103</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.00819590931672548</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.820115858077746</v>
+        <v>2.866846258169299</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.858518476235206</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.83653696673019</v>
+        <v>-4.83266312156908</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8768168651378303</v>
+        <v>0.9250968032938272</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.08989422603525915</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.757851540522498</v>
+        <v>2.804581940614051</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.862616178845835</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.791698565121791</v>
+        <v>-4.787824719960682</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8988499283918183</v>
+        <v>0.9471298665478152</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.08535079309038968</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.764675302900049</v>
+        <v>2.811405702991602</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.81796138867431</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.866777118476913</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.892457200878789</v>
+        <v>-4.88858335571768</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8627074137200972</v>
+        <v>0.9109873518760938</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.1741763618173951</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.715540901294923</v>
+        <v>2.762271301386476</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163219</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.87265672100475</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.848254363792889</v>
+        <v>-4.844380518631779</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8862681510822945</v>
+        <v>0.9345480892382911</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1299735247314946</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.747942206074301</v>
+        <v>2.794672606165854</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.871066721473998</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.885233391456332</v>
+        <v>-4.881359546295222</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8698865404861649</v>
+        <v>0.9181664786421617</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.09299962294016412</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.768536547618347</v>
+        <v>2.8152669477099</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.922314486657037</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.905291470321172</v>
+        <v>-4.901417625160063</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9131110741232682</v>
+        <v>0.961391012279265</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.09299962294016412</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.819784312801386</v>
+        <v>2.866514712892939</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.920755191251291</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.865360797143282</v>
+        <v>-4.861486951982172</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9275240479886775</v>
+        <v>0.9758039861446743</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.05306894976227378</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.842183421302374</v>
+        <v>2.888913821393927</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232398</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.915703419489561</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.824890449580577</v>
+        <v>-4.821016604419468</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9386604152520295</v>
+        <v>0.9869403534080263</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.01259860219956882</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.861413858078266</v>
+        <v>2.908144258169819</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.932890823582265</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.759666268453372</v>
+        <v>-4.755792423292262</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9819374917956165</v>
+        <v>1.030217429951613</v>
       </c>
       <c r="F1988" t="n">
         <v>0.05262557892763681</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.917735770847295</v>
+        <v>2.964466170938848</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639815</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.928851795881546</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.810160558810428</v>
+        <v>-4.806286713649318</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9577007479520745</v>
+        <v>1.005980686108071</v>
       </c>
       <c r="F1989" t="n">
         <v>0.007604841801562567</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.886684300870931</v>
+        <v>2.933414700962484</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.930108588212786</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.830272214845136</v>
+        <v>-4.826398369684027</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9509128778694316</v>
+        <v>0.9991928160254282</v>
       </c>
       <c r="F1990" t="n">
         <v>0.01863218679898176</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.894557500200623</v>
+        <v>2.941287900292175</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.090666359233997</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.927952794117783</v>
+        <v>-4.924078948956673</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.072398417181584</v>
+        <v>1.120678355337581</v>
       </c>
       <c r="F1991" t="n">
         <v>-0.09207100854120703</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.98869335401772</v>
+        <v>3.035423754109273</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.210779268451814</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.90416122551164</v>
+        <v>-4.90028738035053</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.202027953841858</v>
+        <v>1.250307891997855</v>
       </c>
       <c r="F1992" t="n">
         <v>-0.06827943993506475</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.123081204399222</v>
+        <v>3.169811604490775</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756014</v>
+        <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.202487244465673</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.940915644073362</v>
+        <v>-4.937041798912253</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.179034162431028</v>
+        <v>1.227314100587025</v>
       </c>
       <c r="F1993" t="n">
         <v>-0.06827943993506475</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.114789180413081</v>
+        <v>3.161519580504634</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654188</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.200680440049453</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.936581341016314</v>
+        <v>-4.932707495855205</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.178961079237627</v>
+        <v>1.227241017393623</v>
       </c>
       <c r="F1994" t="n">
         <v>0.08337066338413918</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.203972437988384</v>
+        <v>3.250702838079937</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717114</v>
+        <v>3.796293177717113</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.218234845776244</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.927688879623031</v>
+        <v>-4.923815034461922</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.200072469521731</v>
+        <v>1.248352407677728</v>
       </c>
       <c r="F1995" t="n">
         <v>0.08337066338413918</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.221526843715175</v>
+        <v>3.268257243806728</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.576895451488702</v>
+        <v>3.441795892682903</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.094294814507915</v>
+        <v>3.220075505494589</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.927688879623031</v>
+        <v>-4.826570936926951</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.200072469521731</v>
+        <v>1.289090706410061</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.08337066338413918</v>
+        <v>0.2597712401367135</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.087358611494282</v>
+        <v>3.375938249576617</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240615.xlsx
+++ b/tame_output/ON/bt/strategyON_20240615.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>37.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.1%</t>
+          <t>451.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.2%</t>
+          <t>-639.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-247.3%</t>
+          <t>-249.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-100.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.1%</t>
+          <t>-134.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-198.0%</t>
+          <t>-215.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-108.4%</t>
+          <t>-123.4%</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.49997173944063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.57367402532254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.700417502672488</v>
+        <v>-6.653187745846783</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.28353793772092</v>
+        <v>0.302429840451202</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.259428654373765</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.201028582738637</v>
+        <v>2.208404170479404</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.450567108723414</v>
+        <v>-6.403337351897709</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.376220170284252</v>
+        <v>0.3951120730145341</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.259428654373765</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.193770657722339</v>
+        <v>2.201146245463106</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.274675016255982</v>
+        <v>-6.227445259430276</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4501761307918737</v>
+        <v>0.4690680335221558</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.271721300608377</v>
+        <v>-1.259428654373765</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.197369781242988</v>
+        <v>2.204745368983755</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.103228553233518</v>
+        <v>-6.055998796407812</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5320822220554127</v>
+        <v>0.5509741247856952</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.100274837585914</v>
+        <v>-1.087982191351302</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.31356516511102</v>
+        <v>2.320940752851786</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.878195553564695</v>
+        <v>-5.830965796738989</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6211158995392387</v>
+        <v>0.6400078022695213</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8752418379170909</v>
+        <v>-0.8629491916824789</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.44760544252861</v>
+        <v>2.454981030269377</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.814559811330761</v>
+        <v>-5.767330054505055</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6512649974871301</v>
+        <v>0.6701569002174121</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8116060956831563</v>
+        <v>-0.7993134494485443</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.490481688923288</v>
+        <v>2.497857276664055</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.770797630024919</v>
+        <v>-5.723567873199213</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.649964128793262</v>
+        <v>0.6688560315235446</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8116060956831563</v>
+        <v>-0.7993134494485443</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.471675947707084</v>
+        <v>2.479051535447851</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.530367133220059</v>
+        <v>-5.483137376394353</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7478794041400838</v>
+        <v>0.7667713068703659</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5711755988782961</v>
+        <v>-0.558882952643684</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.617677322414877</v>
+        <v>2.625052910155644</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.458124565048864</v>
+        <v>-5.410894808223158</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7807057452433819</v>
+        <v>0.7995976479736639</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5711755988782961</v>
+        <v>-0.558882952643684</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.621606636249697</v>
+        <v>2.628982223990465</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.405126242767476</v>
+        <v>-5.357896485941771</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.802583658073277</v>
+        <v>0.8214755608035591</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5158393398763572</v>
+        <v>-0.5035466936417452</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.655486975568201</v>
+        <v>2.662862563308968</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.296321357287749</v>
+        <v>-5.249091600462044</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8431036834851611</v>
+        <v>0.8619955862154436</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5158393398763572</v>
+        <v>-0.5035466936417452</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.652485046788194</v>
+        <v>2.659860634528961</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.076300559250739</v>
+        <v>-5.029070802425033</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9326910397105794</v>
+        <v>0.9515829424408619</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.374619494808377</v>
+        <v>-0.362326848573765</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.738795990839597</v>
+        <v>2.746171578580364</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.943432870187461</v>
+        <v>-4.896203113361755</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.001732298137714</v>
+        <v>1.020624200867996</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.374619494808377</v>
+        <v>-0.362326848573765</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.75469017364142</v>
+        <v>2.762065761382187</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.823259786822963</v>
+        <v>-4.776030029997257</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.050947375923815</v>
+        <v>1.069839278654098</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.254446411443878</v>
+        <v>-0.242153765209266</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.827939868100421</v>
+        <v>2.835315455841188</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.678587641723225</v>
+        <v>-4.631357884897519</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.11890433652515</v>
+        <v>1.137796239255433</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1097742663441406</v>
+        <v>-0.0974816201095286</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.924831257721703</v>
+        <v>2.932206845462471</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.738462469080917</v>
+        <v>-4.691232712255212</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.080991896983499</v>
+        <v>1.099883799713781</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1696490937018327</v>
+        <v>-0.1573564474672207</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.874943852708514</v>
+        <v>2.882319440449281</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.651662971301908</v>
+        <v>-4.604433214476202</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.138112189417669</v>
+        <v>1.157004092147951</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1696490937018327</v>
+        <v>-0.1573564474672207</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.89734434603108</v>
+        <v>2.904719933771847</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.045936603717144</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.654132677763714</v>
+        <v>-4.606902920938008</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.183927108297911</v>
+        <v>1.156088610936641</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1721188001636389</v>
+        <v>-0.1598261539290269</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.942665323618961</v>
+        <v>2.903310511268176</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.056943526191847</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.722502864087724</v>
+        <v>-4.675273107262019</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.16758595624301</v>
+        <v>1.139747458881739</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1505504548928119</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.959237665515392</v>
+        <v>2.919882853164607</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.047380234823738</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.831041045003858</v>
+        <v>-4.783811288178152</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.114607392508447</v>
+        <v>1.086768895147177</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1505504548928119</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.949674374147284</v>
+        <v>2.910319561796498</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.872089799864125</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.862034204332564</v>
+        <v>-4.814804447506858</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9269196938173518</v>
+        <v>0.8990811964560812</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1505504548928119</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.774383939187671</v>
+        <v>2.735029126836885</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.876657031855912</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.686559944540095</v>
+        <v>-4.639330187714389</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.001676629726127</v>
+        <v>0.9738381323648566</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1505504548928119</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.778951171179458</v>
+        <v>2.739596358828673</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.852399060617119</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.797496197181344</v>
+        <v>-4.750266440355638</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9330441574308346</v>
+        <v>0.9052056600695639</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.162843101127424</v>
+        <v>-0.1505504548928119</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.754693199940665</v>
+        <v>2.71533838758988</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.77321029711129</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.855530445837025</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.805778271326402</v>
+        <v>-4.758548514500696</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9328627129927167</v>
+        <v>0.9050242156314461</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.1588325290378703</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.752855340673536</v>
+        <v>2.71350052832275</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264159</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.865702832269157</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.745925652122679</v>
+        <v>-4.698695895296973</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9669761471063385</v>
+        <v>0.9391376497450679</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.1588325290378703</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.763027727105668</v>
+        <v>2.723672914754883</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742295</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.860649102843018</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.659682189096301</v>
+        <v>-4.612452432270596</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9964198028907498</v>
+        <v>0.9685813055294792</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1711251752724823</v>
+        <v>-0.1588325290378703</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.757973997679529</v>
+        <v>2.718619185328743</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.852424878287543</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.704989008495281</v>
+        <v>-4.657759251669575</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9700728505756835</v>
+        <v>0.9422343532144128</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2119353382817131</v>
+        <v>-0.1996426920471011</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.725263675318516</v>
+        <v>2.68590886296773</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.852976751320645</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.734022113197582</v>
+        <v>-4.686792356371877</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9590114817278645</v>
+        <v>0.9311729843665939</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2119353382817131</v>
+        <v>-0.1996426920471011</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.725815548351617</v>
+        <v>2.686460736000831</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.78224944321201</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.641211631746723</v>
+        <v>-4.593981874921017</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.925408366199574</v>
+        <v>0.8975698688383034</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1191248568308538</v>
+        <v>-0.1068322105962418</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.710774529113499</v>
+        <v>2.671419716762713</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.784122919136611</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.68560110107615</v>
+        <v>-4.638371344250444</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.909526054392404</v>
+        <v>0.8816875570311333</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1635143261602814</v>
+        <v>-0.1512216799256694</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.686014323440443</v>
+        <v>2.646659511089657</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.779198627648334</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.5729298828399</v>
+        <v>-4.525700126014194</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9496702501986269</v>
+        <v>0.9218317528373563</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.05084310792403124</v>
+        <v>-0.03855046168941922</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.748692762893916</v>
+        <v>2.70933795054313</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.784689923479001</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.564109821203878</v>
+        <v>-4.413323124831521</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9586895706837029</v>
+        <v>0.9722738491410927</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.05084310792403124</v>
+        <v>-0.03855046168941922</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.754184058724583</v>
+        <v>2.714829246373797</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.796187125247541</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.762344390090609</v>
+        <v>-4.611557693718252</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8908929448975496</v>
+        <v>0.9044772233549394</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2490776768107618</v>
+        <v>-0.2367850305761498</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.646740519161084</v>
+        <v>2.607385706810298</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705321</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.634542845248194</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.845345671115888</v>
+        <v>-4.694558974743531</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6960481524880913</v>
+        <v>0.7096324309454811</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2676485613379356</v>
+        <v>-0.2553559151033236</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.473953708445433</v>
+        <v>2.434598896094647</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.754692505967399</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.953959749559219</v>
+        <v>-4.803173053186862</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7727521818299645</v>
+        <v>0.7863364602873544</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2676485613379356</v>
+        <v>-0.2553559151033236</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.594103369164638</v>
+        <v>2.554748556813853</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.769205532069722</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.040558332540322</v>
+        <v>-4.889771636167965</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7526257747398462</v>
+        <v>0.7662100531972362</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2676485613379356</v>
+        <v>-0.2553559151033236</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.608616395266961</v>
+        <v>2.569261582916176</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117406991342</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.766624973412091</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.002174669982171</v>
+        <v>-4.851387973609814</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7653986811054754</v>
+        <v>0.7789829595628652</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2292648987797844</v>
+        <v>-0.2169722525451724</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.629066034144221</v>
+        <v>2.589711221793435</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753248</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.763354002257393</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.825058339947005</v>
+        <v>-4.674271643574648</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8329742419648438</v>
+        <v>0.8465585204222337</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2292648987797844</v>
+        <v>-0.2169722525451724</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.625795062989523</v>
+        <v>2.586440250638737</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793897</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.764037394019306</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.870150584780551</v>
+        <v>-4.719363888408194</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8156207357933385</v>
+        <v>0.8292050142507286</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2911609419491742</v>
+        <v>-0.2788682957145622</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.589340828849802</v>
+        <v>2.549986016499016</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.757824369325721</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.690775163541783</v>
+        <v>-4.539988467169426</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8811578795952599</v>
+        <v>0.89474215805265</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1343841837784555</v>
+        <v>-0.1220915375438435</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.677193859058647</v>
+        <v>2.637839046707862</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.73863182465731</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.735789377062389</v>
+        <v>-4.585002680690032</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8439596495186075</v>
+        <v>0.8575439279759973</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1647330790930601</v>
+        <v>-0.1524404328584481</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.639791977201475</v>
+        <v>2.600437164850689</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.744323386996256</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.002793887334824</v>
+        <v>-4.852007190962467</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7428494077485792</v>
+        <v>0.7564336862059691</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3590961171360087</v>
+        <v>-0.3468034709013967</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.528865716714651</v>
+        <v>2.489510904363865</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.743527308892757</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.103991668771997</v>
+        <v>-4.953204972399639</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7015742170702115</v>
+        <v>0.7151584955276014</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4275049306813279</v>
+        <v>-0.4152122844467159</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.487024350483961</v>
+        <v>2.447669538133175</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.741127270447074</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.071516082601224</v>
+        <v>-4.920729386228867</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7121644130928373</v>
+        <v>0.7257486915502271</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4275049306813279</v>
+        <v>-0.4152122844467159</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.484624312038278</v>
+        <v>2.445269499687492</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.737651989655319</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.052477954893927</v>
+        <v>-4.90169125852157</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.716304383384001</v>
+        <v>0.7298886618413909</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4856885420125224</v>
+        <v>-0.4733958957779104</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.446238864447806</v>
+        <v>2.40688405209702</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.915233858594</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.083604586044546</v>
+        <v>-4.932817889672188</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8814355998624341</v>
+        <v>0.895019878319824</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4856885420125224</v>
+        <v>-0.4733958957779104</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.623820733386486</v>
+        <v>2.584465921035701</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.916067187580133</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.135924966645337</v>
+        <v>-4.959052371629252</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8613407766082508</v>
+        <v>0.885359414523132</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4507416820036503</v>
+        <v>-0.5134527550049732</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.645622178377943</v>
+        <v>2.561265134485597</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.922075717977059</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.156182265174295</v>
+        <v>-4.97930967015821</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8592463875935938</v>
+        <v>0.8832650255084746</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4507416820036503</v>
+        <v>-0.5134527550049732</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.651630708774869</v>
+        <v>2.567273664882523</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.001228365769081</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.008439294939293</v>
+        <v>-4.831566699923208</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9974962234796168</v>
+        <v>1.021514861394498</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2829343247687671</v>
+        <v>-0.3456453977700901</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.831467770907821</v>
+        <v>2.747110727015474</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.004021987300562</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.110453977470514</v>
+        <v>-4.933581382454429</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9594839719986092</v>
+        <v>0.98350260991349</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2829343247687671</v>
+        <v>-0.3456453977700901</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.834261392439302</v>
+        <v>2.749904348546955</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.00468433569222</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.10430127141773</v>
+        <v>-4.927428676401645</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9626074028113814</v>
+        <v>0.9866260407262621</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2767816187159828</v>
+        <v>-0.3394926917173058</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.838615364462631</v>
+        <v>2.754258320570284</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.003764812432331</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.121110569568232</v>
+        <v>-4.944237974552147</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9549641602912908</v>
+        <v>0.9789827982061716</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2935909168664845</v>
+        <v>-0.3563019898678074</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.82761026231244</v>
+        <v>2.743253218420094</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.070100366229152</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.058812570792109</v>
+        <v>-4.881939975776024</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.04621891359856</v>
+        <v>1.070237551513441</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2935909168664845</v>
+        <v>-0.3563019898678074</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.893945816109261</v>
+        <v>2.809588772216914</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.77868123861855</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.857022373126951</v>
+        <v>-4.680149778110867</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8355158650540218</v>
+        <v>0.8595345029689028</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.09557272469733008</v>
+        <v>-0.158283797698653</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.721337603800152</v>
+        <v>2.636980559907805</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.848971470940725</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.797131691484358</v>
+        <v>-4.620259096468273</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9297623700332343</v>
+        <v>0.9537810079481153</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.0356820430547366</v>
+        <v>-0.09839311605605955</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.827562245107883</v>
+        <v>2.743205201215536</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.863599207056768</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.894872236109332</v>
+        <v>-4.717999641093248</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9052938882992883</v>
+        <v>0.929312526214169</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05157132118771679</v>
+        <v>-0.1142823941890397</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.832656414344139</v>
+        <v>2.748299370451792</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.86213518788144</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.071209996232262</v>
+        <v>-4.894337401216177</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8332947650747879</v>
+        <v>0.8573134029896692</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2279090813106462</v>
+        <v>-0.2906201543119691</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.725389739095053</v>
+        <v>2.641032695202706</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.860626805921369</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.999663673455385</v>
+        <v>-4.8227910784393</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8604049122254676</v>
+        <v>0.8844235501403483</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2279090813106462</v>
+        <v>-0.2906201543119691</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.723881357134981</v>
+        <v>2.639524313242635</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.860489673356805</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.955290541816816</v>
+        <v>-4.778417946800731</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8780170323163312</v>
+        <v>0.902035670231212</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1835359496720776</v>
+        <v>-0.2462470226734005</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.750368103553559</v>
+        <v>2.666011059661212</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.860489673356805</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.947336571522044</v>
+        <v>-4.770463976505959</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8811986204342399</v>
+        <v>0.9052172583491209</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1835359496720776</v>
+        <v>-0.2462470226734005</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.750368103553559</v>
+        <v>2.666011059661212</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.866871430384609</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.899680840960988</v>
+        <v>-4.722808245944903</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9066426696864669</v>
+        <v>0.9306613076013479</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1358802191110219</v>
+        <v>-0.1985912921123449</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.785343298917997</v>
+        <v>2.70098625502565</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.871763803759334</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.771996531166692</v>
+        <v>-4.595123936150607</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9626087669789103</v>
+        <v>0.9866274048937913</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.00819590931672548</v>
+        <v>-0.07090698231804843</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.866846258169299</v>
+        <v>2.782489214276953</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.858518476235206</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.83266312156908</v>
+        <v>-4.655790526552996</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9250968032938272</v>
+        <v>0.9491154412087077</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.08989422603525915</v>
+        <v>-0.1526052990365821</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.804581940614051</v>
+        <v>2.720224896721704</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690025</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.862616178845835</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.787824719960682</v>
+        <v>-4.610952124944598</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9471298665478152</v>
+        <v>0.9711485044626957</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.08535079309038968</v>
+        <v>-0.1480618660917126</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.811405702991602</v>
+        <v>2.727048659099255</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81796138867431</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.866777118476913</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.88858335571768</v>
+        <v>-4.711710760701596</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9109873518760938</v>
+        <v>0.9350059897909744</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1741763618173951</v>
+        <v>-0.236887434818718</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.762271301386476</v>
+        <v>2.677914257494129</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163219</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.87265672100475</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.844380518631779</v>
+        <v>-4.667507923615696</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9345480892382911</v>
+        <v>0.9585667271531717</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1299735247314946</v>
+        <v>-0.1926845977328176</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.794672606165854</v>
+        <v>2.710315562273507</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022904</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.871066721473998</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.881359546295222</v>
+        <v>-4.704486951279138</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9181664786421617</v>
+        <v>0.9421851165570423</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.09299962294016412</v>
+        <v>-0.1557106959414871</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.8152669477099</v>
+        <v>2.730909903817553</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042138</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.922314486657037</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.901417625160063</v>
+        <v>-4.724545030143979</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.961391012279265</v>
+        <v>0.9854096501941456</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.09299962294016412</v>
+        <v>-0.1557106959414871</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.866514712892939</v>
+        <v>2.782157669000592</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.865367715078279</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.920755191251291</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.861486951982172</v>
+        <v>-4.684614356966089</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9758039861446743</v>
+        <v>0.9998226240595549</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.05306894976227378</v>
+        <v>-0.1157800227635967</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.888913821393927</v>
+        <v>2.80455677750158</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.915703419489561</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.821016604419468</v>
+        <v>-4.644144009403384</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9869403534080263</v>
+        <v>1.010958991322907</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.01259860219956882</v>
+        <v>-0.07530967520089177</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.908144258169819</v>
+        <v>2.823787214277473</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.84257639416211</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.932890823582265</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.755792423292262</v>
+        <v>-4.578919828276178</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.030217429951613</v>
+        <v>1.054236067866494</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.05262557892763681</v>
+        <v>-0.01008549407368614</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.964466170938848</v>
+        <v>2.880109127046501</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639815</v>
+        <v>3.840090220639816</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.928851795881546</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.806286713649318</v>
+        <v>-4.629414118633234</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.005980686108071</v>
+        <v>1.029999324022952</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.007604841801562567</v>
+        <v>-0.05510623119976038</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.933414700962484</v>
+        <v>2.849057657070137</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.930108588212786</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.826398369684027</v>
+        <v>-4.649525774667943</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9991928160254282</v>
+        <v>1.023211453940309</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.01863218679898176</v>
+        <v>-0.04407888620234118</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.941287900292175</v>
+        <v>2.856930856399829</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.090666359233997</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.924078948956673</v>
+        <v>-4.747206353940589</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.120678355337581</v>
+        <v>1.144696993252461</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.09207100854120703</v>
+        <v>-0.15478208154253</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.035423754109273</v>
+        <v>2.951066710216926</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714881</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.210779268451814</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.90028738035053</v>
+        <v>-4.723414785334446</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.250307891997855</v>
+        <v>1.274326529912735</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.06827943993506475</v>
+        <v>-0.1309905129363877</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.169811604490775</v>
+        <v>3.085454560598429</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.202487244465673</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.937041798912253</v>
+        <v>-4.760169203896169</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.227314100587025</v>
+        <v>1.251332738501906</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.06827943993506475</v>
+        <v>-0.1309905129363877</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.161519580504634</v>
+        <v>3.077162536612288</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.200680440049453</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.932707495855205</v>
+        <v>-4.755834900839121</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.227241017393623</v>
+        <v>1.251259655308504</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.08337066338413918</v>
+        <v>0.02065959038281623</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.250702838079937</v>
+        <v>3.16634579418759</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717113</v>
+        <v>3.796293177717114</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.218234845776244</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.923815034461922</v>
+        <v>-4.746942439445838</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.248352407677728</v>
+        <v>1.272371045592609</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.08337066338413918</v>
+        <v>0.02065959038281623</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.268257243806728</v>
+        <v>3.183900199914381</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.441795892682903</v>
+        <v>3.657002145728309</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.220075505494589</v>
+        <v>3.173345105403036</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.826570936926951</v>
+        <v>-4.775529722984789</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.289090706410061</v>
+        <v>1.262776791895373</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2597712401367135</v>
+        <v>0.08883358850191275</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.375938249576617</v>
+        <v>3.226645258504184</v>
       </c>
     </row>
   </sheetData>
